--- a/New_CenterOfRotation/Finite_COR/Data Files/C45_Data/Model 4 Y_Z Data.xlsx
+++ b/New_CenterOfRotation/Finite_COR/Data Files/C45_Data/Model 4 Y_Z Data.xlsx
@@ -4,7 +4,7 @@
   <fileVersion rupBuild="9303" lowestEdited="5" lastEdited="5" appName="xl"/>
   <workbookPr/>
   <bookViews>
-    <workbookView xWindow="480" yWindow="60" windowWidth="18195" windowHeight="8505" activeTab="1"/>
+    <workbookView xWindow="480" yWindow="60" windowWidth="18195" windowHeight="8505" activeTab="2"/>
   </bookViews>
   <sheets>
     <sheet r:id="rId1" sheetId="1" name="4N"/>
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="186" uniqueCount="23">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="180" uniqueCount="22">
   <si>
     <t>Node 25454</t>
   </si>
@@ -86,16 +86,13 @@
   <si>
     <t>X (U1)</t>
   </si>
-  <si>
-    <t/>
-  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" mc:Ignorable="x14ac">
   <numFmts count="0"/>
-  <fonts count="5" x14ac:knownFonts="1">
+  <fonts count="6" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -112,6 +109,12 @@
     <font>
       <sz val="11"/>
       <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
       <name val="Calibri"/>
       <family val="2"/>
     </font>
@@ -180,7 +183,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="29">
+  <cellXfs count="30">
     <xf xfId="0" numFmtId="0" borderId="0" fontId="0" fillId="0"/>
     <xf xfId="0" numFmtId="3" applyNumberFormat="1" borderId="1" applyBorder="1" fontId="1" applyFont="1" fillId="0" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -210,48 +213,54 @@
       <alignment horizontal="right"/>
     </xf>
     <xf xfId="0" numFmtId="0" borderId="0" fontId="0" fillId="0" applyAlignment="1">
-      <alignment horizontal="general"/>
+      <alignment horizontal="left"/>
+    </xf>
+    <xf xfId="0" numFmtId="3" applyNumberFormat="1" borderId="1" applyBorder="1" fontId="2" applyFont="1" fillId="0" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf xfId="0" numFmtId="4" applyNumberFormat="1" borderId="1" applyBorder="1" fontId="2" applyFont="1" fillId="0" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf xfId="0" numFmtId="4" applyNumberFormat="1" borderId="1" applyBorder="1" fontId="2" applyFont="1" fillId="0" applyAlignment="1">
+      <alignment horizontal="left"/>
     </xf>
     <xf xfId="0" numFmtId="0" borderId="0" fontId="0" fillId="0" applyAlignment="1">
       <alignment horizontal="general"/>
     </xf>
-    <xf xfId="0" numFmtId="3" applyNumberFormat="1" borderId="0" fontId="0" fillId="0" applyAlignment="1">
-      <alignment horizontal="general"/>
-    </xf>
-    <xf xfId="0" numFmtId="4" applyNumberFormat="1" borderId="0" fontId="0" fillId="0" applyAlignment="1">
-      <alignment horizontal="general"/>
-    </xf>
-    <xf xfId="0" numFmtId="3" applyNumberFormat="1" borderId="2" applyBorder="1" fontId="2" applyFont="1" fillId="2" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf xfId="0" numFmtId="4" applyNumberFormat="1" borderId="2" applyBorder="1" fontId="2" applyFont="1" fillId="2" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left"/>
+    <xf xfId="0" numFmtId="3" applyNumberFormat="1" borderId="1" applyBorder="1" fontId="2" applyFont="1" fillId="0" applyAlignment="1">
+      <alignment horizontal="right"/>
     </xf>
     <xf xfId="0" numFmtId="3" applyNumberFormat="1" borderId="2" applyBorder="1" fontId="3" applyFont="1" fillId="2" applyFill="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf xfId="0" numFmtId="3" applyNumberFormat="1" borderId="2" applyBorder="1" fontId="3" applyFont="1" fillId="3" applyFill="1" applyAlignment="1">
+    <xf xfId="0" numFmtId="4" applyNumberFormat="1" borderId="2" applyBorder="1" fontId="3" applyFont="1" fillId="2" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf xfId="0" numFmtId="3" applyNumberFormat="1" borderId="2" applyBorder="1" fontId="4" applyFont="1" fillId="2" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf xfId="0" numFmtId="3" applyNumberFormat="1" borderId="2" applyBorder="1" fontId="4" applyFont="1" fillId="3" applyFill="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf xfId="0" numFmtId="3" applyNumberFormat="1" borderId="2" applyBorder="1" fontId="1" applyFont="1" fillId="3" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf xfId="0" numFmtId="3" applyNumberFormat="1" borderId="1" applyBorder="1" fontId="3" applyFont="1" fillId="0" applyAlignment="1">
+    <xf xfId="0" numFmtId="3" applyNumberFormat="1" borderId="1" applyBorder="1" fontId="4" applyFont="1" fillId="0" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf xfId="0" numFmtId="3" applyNumberFormat="1" borderId="1" applyBorder="1" fontId="3" applyFont="1" fillId="0" applyAlignment="1">
+    <xf xfId="0" numFmtId="3" applyNumberFormat="1" borderId="1" applyBorder="1" fontId="4" applyFont="1" fillId="0" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf xfId="0" numFmtId="4" applyNumberFormat="1" borderId="1" applyBorder="1" fontId="5" applyFont="1" fillId="0" applyAlignment="1">
+      <alignment horizontal="right"/>
     </xf>
     <xf xfId="0" numFmtId="4" applyNumberFormat="1" borderId="1" applyBorder="1" fontId="4" applyFont="1" fillId="0" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf xfId="0" numFmtId="4" applyNumberFormat="1" borderId="1" applyBorder="1" fontId="3" applyFont="1" fillId="0" applyAlignment="1">
-      <alignment horizontal="right"/>
+    <xf xfId="0" numFmtId="4" applyNumberFormat="1" borderId="1" applyBorder="1" fontId="4" applyFont="1" fillId="0" applyAlignment="1">
+      <alignment horizontal="left"/>
     </xf>
     <xf xfId="0" numFmtId="4" applyNumberFormat="1" borderId="1" applyBorder="1" fontId="3" applyFont="1" fillId="0" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf xfId="0" numFmtId="4" applyNumberFormat="1" borderId="1" applyBorder="1" fontId="2" applyFont="1" fillId="0" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
     <xf xfId="0" numFmtId="3" applyNumberFormat="1" borderId="0" fontId="0" fillId="0" applyAlignment="1">
@@ -260,11 +269,8 @@
     <xf xfId="0" numFmtId="4" applyNumberFormat="1" borderId="0" fontId="0" fillId="0" applyAlignment="1">
       <alignment horizontal="general"/>
     </xf>
-    <xf xfId="0" numFmtId="3" applyNumberFormat="1" borderId="2" applyBorder="1" fontId="3" applyFont="1" fillId="3" applyFill="1" quotePrefix="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf xfId="0" numFmtId="3" applyNumberFormat="1" borderId="2" applyBorder="1" fontId="1" applyFont="1" fillId="3" applyFill="1" quotePrefix="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+    <xf xfId="0" numFmtId="0" borderId="0" fontId="0" fillId="0" applyAlignment="1">
+      <alignment horizontal="general"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -3421,248 +3427,236 @@
   <dimension ref="A1:AC27"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" style="25" width="13.576428571428572" customWidth="1" bestFit="1"/>
-    <col min="2" max="2" style="26" width="13.576428571428572" customWidth="1" bestFit="1"/>
-    <col min="3" max="3" style="26" width="9.43357142857143" customWidth="1" bestFit="1"/>
-    <col min="4" max="4" style="26" width="13.576428571428572" customWidth="1" bestFit="1"/>
-    <col min="5" max="5" style="10" width="13.576428571428572" customWidth="1" bestFit="1"/>
-    <col min="6" max="6" style="25" width="13.576428571428572" customWidth="1" bestFit="1"/>
-    <col min="7" max="7" style="26" width="13.576428571428572" customWidth="1" bestFit="1"/>
-    <col min="8" max="8" style="26" width="13.576428571428572" customWidth="1" bestFit="1"/>
-    <col min="9" max="9" style="26" width="13.576428571428572" customWidth="1" bestFit="1"/>
-    <col min="10" max="10" style="10" width="13.576428571428572" customWidth="1" bestFit="1"/>
-    <col min="11" max="11" style="25" width="13.576428571428572" customWidth="1" bestFit="1"/>
-    <col min="12" max="12" style="26" width="9.290714285714287" customWidth="1" bestFit="1"/>
-    <col min="13" max="13" style="26" width="13.576428571428572" customWidth="1" bestFit="1"/>
-    <col min="14" max="14" style="26" width="13.576428571428572" customWidth="1" bestFit="1"/>
-    <col min="15" max="15" style="10" width="13.576428571428572" customWidth="1" bestFit="1"/>
-    <col min="16" max="16" style="25" width="13.576428571428572" customWidth="1" bestFit="1"/>
-    <col min="17" max="17" style="26" width="13.576428571428572" customWidth="1" bestFit="1"/>
-    <col min="18" max="18" style="26" width="9.43357142857143" customWidth="1" bestFit="1"/>
-    <col min="19" max="19" style="26" width="13.576428571428572" customWidth="1" bestFit="1"/>
-    <col min="20" max="20" style="10" width="13.576428571428572" customWidth="1" bestFit="1"/>
-    <col min="21" max="21" style="25" width="13.576428571428572" customWidth="1" bestFit="1"/>
-    <col min="22" max="22" style="26" width="13.576428571428572" customWidth="1" bestFit="1"/>
-    <col min="23" max="23" style="26" width="13.576428571428572" customWidth="1" bestFit="1"/>
-    <col min="24" max="24" style="26" width="13.576428571428572" customWidth="1" bestFit="1"/>
-    <col min="25" max="25" style="10" width="13.576428571428572" customWidth="1" bestFit="1"/>
-    <col min="26" max="26" style="25" width="13.576428571428572" customWidth="1" bestFit="1"/>
-    <col min="27" max="27" style="26" width="13.576428571428572" customWidth="1" bestFit="1"/>
-    <col min="28" max="28" style="26" width="9.43357142857143" customWidth="1" bestFit="1"/>
-    <col min="29" max="29" style="26" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="1" max="1" style="27" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="2" max="2" style="28" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="3" max="3" style="28" width="9.43357142857143" customWidth="1" bestFit="1"/>
+    <col min="4" max="4" style="28" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="5" max="5" style="29" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="6" max="6" style="27" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="7" max="7" style="28" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="8" max="8" style="28" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="9" max="9" style="28" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="10" max="10" style="29" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="11" max="11" style="27" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="12" max="12" style="28" width="9.290714285714287" customWidth="1" bestFit="1"/>
+    <col min="13" max="13" style="28" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="14" max="14" style="28" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="15" max="15" style="29" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="16" max="16" style="27" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="17" max="17" style="28" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="18" max="18" style="28" width="9.43357142857143" customWidth="1" bestFit="1"/>
+    <col min="19" max="19" style="28" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="20" max="20" style="29" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="21" max="21" style="27" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="22" max="22" style="28" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="23" max="23" style="28" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="24" max="24" style="28" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="25" max="25" style="29" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="26" max="26" style="27" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="27" max="27" style="28" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="28" max="28" style="28" width="9.43357142857143" customWidth="1" bestFit="1"/>
+    <col min="29" max="29" style="28" width="13.576428571428572" customWidth="1" bestFit="1"/>
   </cols>
   <sheetData>
     <row x14ac:dyDescent="0.25" r="1" customHeight="1" ht="18.75">
-      <c r="A1" s="12" t="s">
+      <c r="A1" s="11" t="s">
         <v>9</v>
       </c>
-      <c r="B1" s="13"/>
+      <c r="B1" s="12"/>
       <c r="C1" s="13" t="s">
         <v>10</v>
       </c>
-      <c r="D1" s="13"/>
-      <c r="E1" s="11"/>
-      <c r="F1" s="12" t="s">
+      <c r="D1" s="12"/>
+      <c r="E1" s="14"/>
+      <c r="F1" s="11" t="s">
         <v>11</v>
       </c>
-      <c r="G1" s="13"/>
-      <c r="H1" s="13"/>
-      <c r="I1" s="13"/>
-      <c r="J1" s="11"/>
-      <c r="K1" s="12"/>
-      <c r="L1" s="13"/>
-      <c r="M1" s="13"/>
-      <c r="N1" s="13"/>
-      <c r="O1" s="11"/>
-      <c r="P1" s="12"/>
-      <c r="Q1" s="13"/>
-      <c r="R1" s="13"/>
-      <c r="S1" s="13"/>
-      <c r="T1" s="11"/>
-      <c r="U1" s="12"/>
-      <c r="V1" s="13"/>
-      <c r="W1" s="13"/>
-      <c r="X1" s="13"/>
-      <c r="Y1" s="11"/>
-      <c r="Z1" s="12"/>
-      <c r="AA1" s="13"/>
-      <c r="AB1" s="13"/>
-      <c r="AC1" s="13"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="2" customHeight="1" ht="18.75">
-      <c r="A2" s="14" t="s">
+      <c r="G1" s="12"/>
+      <c r="H1" s="12"/>
+      <c r="I1" s="12"/>
+      <c r="J1" s="14"/>
+      <c r="K1" s="15"/>
+      <c r="L1" s="12"/>
+      <c r="M1" s="12"/>
+      <c r="N1" s="12"/>
+      <c r="O1" s="14"/>
+      <c r="P1" s="15"/>
+      <c r="Q1" s="12"/>
+      <c r="R1" s="12"/>
+      <c r="S1" s="12"/>
+      <c r="T1" s="14"/>
+      <c r="U1" s="15"/>
+      <c r="V1" s="12"/>
+      <c r="W1" s="12"/>
+      <c r="X1" s="12"/>
+      <c r="Y1" s="14"/>
+      <c r="Z1" s="15"/>
+      <c r="AA1" s="12"/>
+      <c r="AB1" s="12"/>
+      <c r="AC1" s="12"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="2" customHeight="1" ht="19.5">
+      <c r="A2" s="16" t="s">
         <v>12</v>
       </c>
-      <c r="B2" s="15"/>
-      <c r="C2" s="15"/>
-      <c r="D2" s="15"/>
-      <c r="E2" s="11"/>
-      <c r="F2" s="16" t="s">
+      <c r="B2" s="17"/>
+      <c r="C2" s="17"/>
+      <c r="D2" s="17"/>
+      <c r="E2" s="14"/>
+      <c r="F2" s="18" t="s">
         <v>13</v>
       </c>
-      <c r="G2" s="15"/>
-      <c r="H2" s="15"/>
-      <c r="I2" s="15"/>
-      <c r="J2" s="11"/>
-      <c r="K2" s="14" t="s">
+      <c r="G2" s="17"/>
+      <c r="H2" s="17"/>
+      <c r="I2" s="17"/>
+      <c r="J2" s="14"/>
+      <c r="K2" s="16" t="s">
         <v>14</v>
       </c>
-      <c r="L2" s="15"/>
-      <c r="M2" s="15"/>
-      <c r="N2" s="15"/>
-      <c r="O2" s="11"/>
-      <c r="P2" s="16" t="s">
+      <c r="L2" s="17"/>
+      <c r="M2" s="17"/>
+      <c r="N2" s="17"/>
+      <c r="O2" s="14"/>
+      <c r="P2" s="18" t="s">
         <v>15</v>
       </c>
-      <c r="Q2" s="15"/>
-      <c r="R2" s="15"/>
-      <c r="S2" s="15"/>
-      <c r="T2" s="11"/>
-      <c r="U2" s="14" t="s">
+      <c r="Q2" s="17"/>
+      <c r="R2" s="17"/>
+      <c r="S2" s="17"/>
+      <c r="T2" s="14"/>
+      <c r="U2" s="16" t="s">
         <v>16</v>
       </c>
-      <c r="V2" s="15"/>
-      <c r="W2" s="15"/>
-      <c r="X2" s="15"/>
-      <c r="Y2" s="11"/>
-      <c r="Z2" s="14" t="s">
+      <c r="V2" s="17"/>
+      <c r="W2" s="17"/>
+      <c r="X2" s="17"/>
+      <c r="Y2" s="14"/>
+      <c r="Z2" s="16" t="s">
         <v>17</v>
       </c>
-      <c r="AA2" s="15"/>
-      <c r="AB2" s="15"/>
-      <c r="AC2" s="15"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="3" customHeight="1" ht="14.449999999999998">
-      <c r="A3" s="27" t="s">
-        <v>22</v>
-      </c>
+      <c r="AA2" s="17"/>
+      <c r="AB2" s="17"/>
+      <c r="AC2" s="17"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="3" customHeight="1" ht="18.75">
+      <c r="A3" s="19"/>
       <c r="B3" s="6">
         <v>25454</v>
       </c>
-      <c r="C3" s="13"/>
+      <c r="C3" s="12"/>
       <c r="D3" s="5"/>
       <c r="E3" s="3"/>
-      <c r="F3" s="27" t="s">
-        <v>22</v>
-      </c>
+      <c r="F3" s="19"/>
       <c r="G3" s="6">
         <v>31067</v>
       </c>
       <c r="H3" s="5"/>
       <c r="I3" s="5"/>
       <c r="J3" s="3"/>
-      <c r="K3" s="27" t="s">
-        <v>22</v>
-      </c>
+      <c r="K3" s="19"/>
       <c r="L3" s="1">
         <v>29005</v>
       </c>
       <c r="M3" s="2"/>
       <c r="N3" s="2"/>
       <c r="O3" s="3"/>
-      <c r="P3" s="27" t="s">
-        <v>22</v>
-      </c>
+      <c r="P3" s="19"/>
       <c r="Q3" s="1">
         <v>45615</v>
       </c>
       <c r="R3" s="2"/>
       <c r="S3" s="2"/>
       <c r="T3" s="3"/>
-      <c r="U3" s="27" t="s">
-        <v>22</v>
-      </c>
+      <c r="U3" s="19"/>
       <c r="V3" s="1">
         <v>52027</v>
       </c>
       <c r="W3" s="2"/>
       <c r="X3" s="2"/>
       <c r="Y3" s="3"/>
-      <c r="Z3" s="28" t="s">
-        <v>22</v>
-      </c>
-      <c r="AA3" s="19">
+      <c r="Z3" s="20"/>
+      <c r="AA3" s="21">
         <v>49903</v>
       </c>
       <c r="AB3" s="2"/>
       <c r="AC3" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="4" customHeight="1" ht="18.75">
-      <c r="A4" s="20" t="s">
+    <row x14ac:dyDescent="0.25" r="4" customHeight="1" ht="19.5">
+      <c r="A4" s="22" t="s">
         <v>20</v>
       </c>
       <c r="B4" s="7">
         <v>-6.65384</v>
       </c>
-      <c r="C4" s="21">
+      <c r="C4" s="23">
         <v>441.175</v>
       </c>
       <c r="D4" s="7">
         <v>-709.18</v>
       </c>
       <c r="E4" s="3"/>
-      <c r="F4" s="20" t="s">
+      <c r="F4" s="22" t="s">
         <v>20</v>
       </c>
       <c r="G4" s="7">
         <v>6.11839</v>
       </c>
-      <c r="H4" s="22">
+      <c r="H4" s="24">
         <v>439.835</v>
       </c>
       <c r="I4" s="7">
         <v>-709.539</v>
       </c>
       <c r="J4" s="3"/>
-      <c r="K4" s="20" t="s">
+      <c r="K4" s="22" t="s">
         <v>20</v>
       </c>
       <c r="L4" s="2">
         <v>0.185553</v>
       </c>
-      <c r="M4" s="22">
+      <c r="M4" s="24">
         <v>446.547</v>
       </c>
       <c r="N4" s="2">
         <v>-707.74</v>
       </c>
       <c r="O4" s="3"/>
-      <c r="P4" s="20" t="s">
+      <c r="P4" s="22" t="s">
         <v>20</v>
       </c>
       <c r="Q4" s="2">
         <v>-8.27627</v>
       </c>
-      <c r="R4" s="21">
+      <c r="R4" s="23">
         <v>440.046</v>
       </c>
       <c r="S4" s="2">
         <v>-714.179</v>
       </c>
       <c r="T4" s="3"/>
-      <c r="U4" s="20" t="s">
+      <c r="U4" s="22" t="s">
         <v>20</v>
       </c>
       <c r="V4" s="2">
         <v>7.72579</v>
       </c>
-      <c r="W4" s="22">
+      <c r="W4" s="24">
         <v>440.224</v>
       </c>
       <c r="X4" s="2">
         <v>-714.622</v>
       </c>
       <c r="Y4" s="3"/>
-      <c r="Z4" s="20" t="s">
+      <c r="Z4" s="22" t="s">
         <v>20</v>
       </c>
-      <c r="AA4" s="22">
+      <c r="AA4" s="24">
         <v>-0.0172085</v>
       </c>
-      <c r="AB4" s="21">
+      <c r="AB4" s="23">
         <v>445.307</v>
       </c>
-      <c r="AC4" s="22">
+      <c r="AC4" s="24">
         <v>-714.355</v>
       </c>
     </row>
@@ -3670,7 +3664,7 @@
       <c r="A5" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="B5" s="23" t="s">
+      <c r="B5" s="25" t="s">
         <v>21</v>
       </c>
       <c r="C5" s="5" t="s">
@@ -3683,7 +3677,7 @@
       <c r="F5" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="G5" s="23" t="s">
+      <c r="G5" s="25" t="s">
         <v>21</v>
       </c>
       <c r="H5" s="5" t="s">
@@ -3696,7 +3690,7 @@
       <c r="K5" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="L5" s="23" t="s">
+      <c r="L5" s="25" t="s">
         <v>21</v>
       </c>
       <c r="M5" s="5" t="s">
@@ -3709,7 +3703,7 @@
       <c r="P5" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="Q5" s="23" t="s">
+      <c r="Q5" s="25" t="s">
         <v>21</v>
       </c>
       <c r="R5" s="5" t="s">
@@ -3722,7 +3716,7 @@
       <c r="U5" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="V5" s="23" t="s">
+      <c r="V5" s="25" t="s">
         <v>21</v>
       </c>
       <c r="W5" s="5" t="s">
@@ -3735,7 +3729,7 @@
       <c r="Z5" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="AA5" s="23" t="s">
+      <c r="AA5" s="25" t="s">
         <v>21</v>
       </c>
       <c r="AB5" s="5" t="s">
@@ -5405,35 +5399,35 @@
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="27" customHeight="1" ht="18.75">
-      <c r="A27" s="12"/>
-      <c r="B27" s="13"/>
-      <c r="C27" s="13"/>
-      <c r="D27" s="13"/>
-      <c r="E27" s="11"/>
-      <c r="F27" s="12"/>
-      <c r="G27" s="13"/>
-      <c r="H27" s="13"/>
-      <c r="I27" s="13"/>
-      <c r="J27" s="11"/>
-      <c r="K27" s="12"/>
-      <c r="L27" s="13"/>
-      <c r="M27" s="13"/>
-      <c r="N27" s="13"/>
-      <c r="O27" s="11"/>
-      <c r="P27" s="12"/>
-      <c r="Q27" s="13"/>
-      <c r="R27" s="13"/>
-      <c r="S27" s="13"/>
-      <c r="T27" s="11"/>
-      <c r="U27" s="12"/>
-      <c r="V27" s="13"/>
-      <c r="W27" s="13"/>
-      <c r="X27" s="13"/>
-      <c r="Y27" s="11"/>
-      <c r="Z27" s="12"/>
-      <c r="AA27" s="13"/>
-      <c r="AB27" s="13"/>
-      <c r="AC27" s="13"/>
+      <c r="A27" s="15"/>
+      <c r="B27" s="12"/>
+      <c r="C27" s="12"/>
+      <c r="D27" s="12"/>
+      <c r="E27" s="14"/>
+      <c r="F27" s="15"/>
+      <c r="G27" s="12"/>
+      <c r="H27" s="12"/>
+      <c r="I27" s="12"/>
+      <c r="J27" s="14"/>
+      <c r="K27" s="15"/>
+      <c r="L27" s="12"/>
+      <c r="M27" s="12"/>
+      <c r="N27" s="12"/>
+      <c r="O27" s="14"/>
+      <c r="P27" s="15"/>
+      <c r="Q27" s="12"/>
+      <c r="R27" s="12"/>
+      <c r="S27" s="12"/>
+      <c r="T27" s="14"/>
+      <c r="U27" s="15"/>
+      <c r="V27" s="12"/>
+      <c r="W27" s="12"/>
+      <c r="X27" s="12"/>
+      <c r="Y27" s="14"/>
+      <c r="Z27" s="15"/>
+      <c r="AA27" s="12"/>
+      <c r="AB27" s="12"/>
+      <c r="AC27" s="12"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -5445,2114 +5439,2084 @@
   <sheetPr>
     <outlinePr summaryBelow="0"/>
   </sheetPr>
-  <dimension ref="A1:AD29"/>
+  <dimension ref="A1:AC29"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" style="10" width="2.862142857142857" customWidth="1" bestFit="1"/>
-    <col min="2" max="2" style="25" width="13.576428571428572" customWidth="1" bestFit="1"/>
-    <col min="3" max="3" style="26" width="13.576428571428572" customWidth="1" bestFit="1"/>
-    <col min="4" max="4" style="26" width="13.576428571428572" customWidth="1" bestFit="1"/>
-    <col min="5" max="5" style="26" width="13.576428571428572" customWidth="1" bestFit="1"/>
-    <col min="6" max="6" style="10" width="13.576428571428572" customWidth="1" bestFit="1"/>
-    <col min="7" max="7" style="25" width="13.576428571428572" customWidth="1" bestFit="1"/>
-    <col min="8" max="8" style="26" width="13.576428571428572" customWidth="1" bestFit="1"/>
-    <col min="9" max="9" style="26" width="13.576428571428572" customWidth="1" bestFit="1"/>
-    <col min="10" max="10" style="26" width="13.576428571428572" customWidth="1" bestFit="1"/>
-    <col min="11" max="11" style="10" width="13.576428571428572" customWidth="1" bestFit="1"/>
-    <col min="12" max="12" style="25" width="13.576428571428572" customWidth="1" bestFit="1"/>
-    <col min="13" max="13" style="26" width="13.576428571428572" customWidth="1" bestFit="1"/>
-    <col min="14" max="14" style="26" width="13.576428571428572" customWidth="1" bestFit="1"/>
-    <col min="15" max="15" style="26" width="13.576428571428572" customWidth="1" bestFit="1"/>
-    <col min="16" max="16" style="10" width="13.576428571428572" customWidth="1" bestFit="1"/>
-    <col min="17" max="17" style="25" width="13.576428571428572" customWidth="1" bestFit="1"/>
-    <col min="18" max="18" style="26" width="13.576428571428572" customWidth="1" bestFit="1"/>
-    <col min="19" max="19" style="26" width="13.576428571428572" customWidth="1" bestFit="1"/>
-    <col min="20" max="20" style="26" width="13.576428571428572" customWidth="1" bestFit="1"/>
-    <col min="21" max="21" style="10" width="13.576428571428572" customWidth="1" bestFit="1"/>
-    <col min="22" max="22" style="25" width="13.576428571428572" customWidth="1" bestFit="1"/>
-    <col min="23" max="23" style="26" width="13.576428571428572" customWidth="1" bestFit="1"/>
-    <col min="24" max="24" style="26" width="13.576428571428572" customWidth="1" bestFit="1"/>
-    <col min="25" max="25" style="26" width="13.576428571428572" customWidth="1" bestFit="1"/>
-    <col min="26" max="26" style="10" width="13.576428571428572" customWidth="1" bestFit="1"/>
-    <col min="27" max="27" style="25" width="13.576428571428572" customWidth="1" bestFit="1"/>
-    <col min="28" max="28" style="26" width="13.576428571428572" customWidth="1" bestFit="1"/>
-    <col min="29" max="29" style="26" width="13.576428571428572" customWidth="1" bestFit="1"/>
-    <col min="30" max="30" style="26" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="1" max="1" style="27" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="2" max="2" style="28" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="3" max="3" style="28" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="4" max="4" style="28" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="5" max="5" style="29" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="6" max="6" style="27" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="7" max="7" style="28" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="8" max="8" style="28" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="9" max="9" style="28" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="10" max="10" style="29" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="11" max="11" style="27" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="12" max="12" style="28" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="13" max="13" style="28" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="14" max="14" style="28" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="15" max="15" style="29" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="16" max="16" style="27" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="17" max="17" style="28" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="18" max="18" style="28" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="19" max="19" style="28" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="20" max="20" style="29" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="21" max="21" style="27" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="22" max="22" style="28" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="23" max="23" style="28" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="24" max="24" style="28" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="25" max="25" style="29" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="26" max="26" style="27" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="27" max="27" style="28" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="28" max="28" style="28" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="29" max="29" style="28" width="13.576428571428572" customWidth="1" bestFit="1"/>
   </cols>
   <sheetData>
     <row x14ac:dyDescent="0.25" r="1" customHeight="1" ht="18.75">
-      <c r="A1" s="11"/>
-      <c r="B1" s="12" t="s">
+      <c r="A1" s="11" t="s">
         <v>9</v>
       </c>
-      <c r="C1" s="13"/>
-      <c r="D1" s="13" t="s">
+      <c r="B1" s="12"/>
+      <c r="C1" s="13" t="s">
         <v>10</v>
       </c>
-      <c r="E1" s="13"/>
-      <c r="F1" s="11"/>
-      <c r="G1" s="12" t="s">
+      <c r="D1" s="12"/>
+      <c r="E1" s="14"/>
+      <c r="F1" s="11" t="s">
         <v>11</v>
       </c>
-      <c r="H1" s="13"/>
-      <c r="I1" s="13"/>
-      <c r="J1" s="13"/>
-      <c r="K1" s="11"/>
+      <c r="G1" s="12"/>
+      <c r="H1" s="12"/>
+      <c r="I1" s="12"/>
+      <c r="J1" s="14"/>
+      <c r="K1" s="15"/>
       <c r="L1" s="12"/>
-      <c r="M1" s="13"/>
-      <c r="N1" s="13"/>
-      <c r="O1" s="13"/>
-      <c r="P1" s="11"/>
+      <c r="M1" s="12"/>
+      <c r="N1" s="12"/>
+      <c r="O1" s="14"/>
+      <c r="P1" s="15"/>
       <c r="Q1" s="12"/>
-      <c r="R1" s="13"/>
-      <c r="S1" s="13"/>
-      <c r="T1" s="13"/>
-      <c r="U1" s="11"/>
+      <c r="R1" s="12"/>
+      <c r="S1" s="12"/>
+      <c r="T1" s="14"/>
+      <c r="U1" s="15"/>
       <c r="V1" s="12"/>
-      <c r="W1" s="13"/>
-      <c r="X1" s="13"/>
-      <c r="Y1" s="13"/>
-      <c r="Z1" s="11"/>
+      <c r="W1" s="12"/>
+      <c r="X1" s="12"/>
+      <c r="Y1" s="14"/>
+      <c r="Z1" s="15"/>
       <c r="AA1" s="12"/>
-      <c r="AB1" s="13"/>
-      <c r="AC1" s="13"/>
-      <c r="AD1" s="13"/>
+      <c r="AB1" s="12"/>
+      <c r="AC1" s="12"/>
     </row>
     <row x14ac:dyDescent="0.25" r="2" customHeight="1" ht="18.75">
-      <c r="A2" s="11"/>
-      <c r="B2" s="14" t="s">
+      <c r="A2" s="16" t="s">
         <v>12</v>
       </c>
-      <c r="C2" s="15"/>
-      <c r="D2" s="15"/>
-      <c r="E2" s="15"/>
-      <c r="F2" s="11"/>
-      <c r="G2" s="16" t="s">
+      <c r="B2" s="17"/>
+      <c r="C2" s="17"/>
+      <c r="D2" s="17"/>
+      <c r="E2" s="14"/>
+      <c r="F2" s="18" t="s">
         <v>13</v>
       </c>
-      <c r="H2" s="15"/>
-      <c r="I2" s="15"/>
-      <c r="J2" s="15"/>
-      <c r="K2" s="11"/>
-      <c r="L2" s="14" t="s">
+      <c r="G2" s="17"/>
+      <c r="H2" s="17"/>
+      <c r="I2" s="17"/>
+      <c r="J2" s="14"/>
+      <c r="K2" s="16" t="s">
         <v>14</v>
       </c>
-      <c r="M2" s="15"/>
-      <c r="N2" s="15"/>
-      <c r="O2" s="15"/>
-      <c r="P2" s="11"/>
-      <c r="Q2" s="16" t="s">
+      <c r="L2" s="17"/>
+      <c r="M2" s="17"/>
+      <c r="N2" s="17"/>
+      <c r="O2" s="14"/>
+      <c r="P2" s="18" t="s">
         <v>15</v>
       </c>
-      <c r="R2" s="15"/>
-      <c r="S2" s="15"/>
-      <c r="T2" s="15"/>
-      <c r="U2" s="11"/>
-      <c r="V2" s="14" t="s">
+      <c r="Q2" s="17"/>
+      <c r="R2" s="17"/>
+      <c r="S2" s="17"/>
+      <c r="T2" s="14"/>
+      <c r="U2" s="16" t="s">
         <v>16</v>
       </c>
-      <c r="W2" s="15"/>
-      <c r="X2" s="15"/>
-      <c r="Y2" s="15"/>
-      <c r="Z2" s="11"/>
-      <c r="AA2" s="14" t="s">
+      <c r="V2" s="17"/>
+      <c r="W2" s="17"/>
+      <c r="X2" s="17"/>
+      <c r="Y2" s="14"/>
+      <c r="Z2" s="16" t="s">
         <v>17</v>
       </c>
-      <c r="AB2" s="15"/>
-      <c r="AC2" s="15"/>
-      <c r="AD2" s="15"/>
+      <c r="AA2" s="17"/>
+      <c r="AB2" s="17"/>
+      <c r="AC2" s="17"/>
     </row>
     <row x14ac:dyDescent="0.25" r="3" customHeight="1" ht="18.75">
-      <c r="A3" s="11"/>
-      <c r="B3" s="17" t="s">
+      <c r="A3" s="19" t="s">
         <v>18</v>
       </c>
-      <c r="C3" s="6">
+      <c r="B3" s="6">
         <v>25454</v>
       </c>
-      <c r="D3" s="13"/>
-      <c r="E3" s="5"/>
-      <c r="F3" s="3"/>
-      <c r="G3" s="17" t="s">
+      <c r="C3" s="12"/>
+      <c r="D3" s="5"/>
+      <c r="E3" s="3"/>
+      <c r="F3" s="19" t="s">
         <v>18</v>
       </c>
-      <c r="H3" s="6">
+      <c r="G3" s="6">
         <v>31067</v>
       </c>
+      <c r="H3" s="5"/>
       <c r="I3" s="5"/>
-      <c r="J3" s="5"/>
-      <c r="K3" s="3"/>
-      <c r="L3" s="17" t="s">
+      <c r="J3" s="3"/>
+      <c r="K3" s="19" t="s">
         <v>18</v>
       </c>
-      <c r="M3" s="1">
+      <c r="L3" s="1">
         <v>29005</v>
       </c>
+      <c r="M3" s="2"/>
       <c r="N3" s="2"/>
-      <c r="O3" s="2"/>
-      <c r="P3" s="3"/>
-      <c r="Q3" s="17" t="s">
+      <c r="O3" s="3"/>
+      <c r="P3" s="19" t="s">
         <v>18</v>
       </c>
-      <c r="R3" s="1">
+      <c r="Q3" s="1">
         <v>45615</v>
       </c>
+      <c r="R3" s="2"/>
       <c r="S3" s="2"/>
-      <c r="T3" s="2"/>
-      <c r="U3" s="3"/>
-      <c r="V3" s="17" t="s">
+      <c r="T3" s="3"/>
+      <c r="U3" s="19" t="s">
         <v>18</v>
       </c>
-      <c r="W3" s="1">
+      <c r="V3" s="1">
         <v>52027</v>
       </c>
+      <c r="W3" s="2"/>
       <c r="X3" s="2"/>
-      <c r="Y3" s="2"/>
-      <c r="Z3" s="3"/>
-      <c r="AA3" s="18" t="s">
+      <c r="Y3" s="3"/>
+      <c r="Z3" s="20" t="s">
         <v>19</v>
       </c>
-      <c r="AB3" s="19">
+      <c r="AA3" s="21">
         <v>49903</v>
       </c>
+      <c r="AB3" s="2"/>
       <c r="AC3" s="2"/>
-      <c r="AD3" s="2"/>
     </row>
     <row x14ac:dyDescent="0.25" r="4" customHeight="1" ht="19.5">
-      <c r="A4" s="11"/>
-      <c r="B4" s="20" t="s">
+      <c r="A4" s="22" t="s">
         <v>20</v>
       </c>
-      <c r="C4" s="7">
+      <c r="B4" s="7">
         <v>-6.65384</v>
       </c>
-      <c r="D4" s="21">
+      <c r="C4" s="23">
         <v>441.175</v>
       </c>
-      <c r="E4" s="7">
+      <c r="D4" s="7">
         <v>-709.18</v>
       </c>
-      <c r="F4" s="3"/>
-      <c r="G4" s="20" t="s">
+      <c r="E4" s="3"/>
+      <c r="F4" s="22" t="s">
         <v>20</v>
       </c>
-      <c r="H4" s="7">
+      <c r="G4" s="7">
         <v>6.11839</v>
       </c>
-      <c r="I4" s="22">
+      <c r="H4" s="24">
         <v>439.835</v>
       </c>
-      <c r="J4" s="7">
+      <c r="I4" s="7">
         <v>-709.539</v>
       </c>
-      <c r="K4" s="3"/>
-      <c r="L4" s="20" t="s">
+      <c r="J4" s="3"/>
+      <c r="K4" s="22" t="s">
         <v>20</v>
       </c>
-      <c r="M4" s="2">
+      <c r="L4" s="2">
         <v>0.185553</v>
       </c>
-      <c r="N4" s="22">
+      <c r="M4" s="24">
         <v>446.547</v>
       </c>
-      <c r="O4" s="2">
+      <c r="N4" s="2">
         <v>-707.74</v>
       </c>
-      <c r="P4" s="3"/>
-      <c r="Q4" s="20" t="s">
+      <c r="O4" s="3"/>
+      <c r="P4" s="22" t="s">
         <v>20</v>
       </c>
-      <c r="R4" s="2">
+      <c r="Q4" s="2">
         <v>-8.27627</v>
       </c>
-      <c r="S4" s="21">
+      <c r="R4" s="23">
         <v>440.046</v>
       </c>
-      <c r="T4" s="2">
+      <c r="S4" s="2">
         <v>-714.179</v>
       </c>
-      <c r="U4" s="3"/>
-      <c r="V4" s="20" t="s">
+      <c r="T4" s="3"/>
+      <c r="U4" s="22" t="s">
         <v>20</v>
       </c>
-      <c r="W4" s="2">
+      <c r="V4" s="2">
         <v>7.72579</v>
       </c>
-      <c r="X4" s="22">
+      <c r="W4" s="24">
         <v>440.224</v>
       </c>
-      <c r="Y4" s="2">
+      <c r="X4" s="2">
         <v>-714.622</v>
       </c>
-      <c r="Z4" s="3"/>
-      <c r="AA4" s="20" t="s">
+      <c r="Y4" s="3"/>
+      <c r="Z4" s="22" t="s">
         <v>20</v>
       </c>
-      <c r="AB4" s="22">
+      <c r="AA4" s="24">
         <v>-0.0172085</v>
       </c>
-      <c r="AC4" s="21">
+      <c r="AB4" s="23">
         <v>445.307</v>
       </c>
-      <c r="AD4" s="22">
+      <c r="AC4" s="24">
         <v>-714.355</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="5" customHeight="1" ht="18.75">
-      <c r="A5" s="11"/>
-      <c r="B5" s="4" t="s">
+      <c r="A5" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="C5" s="23" t="s">
+      <c r="B5" s="25" t="s">
         <v>21</v>
       </c>
+      <c r="C5" s="5" t="s">
+        <v>7</v>
+      </c>
       <c r="D5" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="E5" s="3"/>
+      <c r="F5" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="G5" s="25" t="s">
+        <v>21</v>
+      </c>
+      <c r="H5" s="5" t="s">
         <v>7</v>
       </c>
-      <c r="E5" s="5" t="s">
+      <c r="I5" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="F5" s="3"/>
-      <c r="G5" s="4" t="s">
+      <c r="J5" s="3"/>
+      <c r="K5" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="H5" s="23" t="s">
+      <c r="L5" s="25" t="s">
         <v>21</v>
       </c>
-      <c r="I5" s="5" t="s">
+      <c r="M5" s="5" t="s">
         <v>7</v>
       </c>
-      <c r="J5" s="5" t="s">
+      <c r="N5" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="K5" s="3"/>
-      <c r="L5" s="4" t="s">
+      <c r="O5" s="3"/>
+      <c r="P5" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="M5" s="23" t="s">
+      <c r="Q5" s="25" t="s">
         <v>21</v>
       </c>
-      <c r="N5" s="5" t="s">
+      <c r="R5" s="5" t="s">
         <v>7</v>
       </c>
-      <c r="O5" s="5" t="s">
+      <c r="S5" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="P5" s="3"/>
-      <c r="Q5" s="4" t="s">
+      <c r="T5" s="3"/>
+      <c r="U5" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="R5" s="23" t="s">
+      <c r="V5" s="25" t="s">
         <v>21</v>
       </c>
-      <c r="S5" s="5" t="s">
+      <c r="W5" s="5" t="s">
         <v>7</v>
       </c>
-      <c r="T5" s="5" t="s">
+      <c r="X5" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="U5" s="3"/>
-      <c r="V5" s="4" t="s">
+      <c r="Y5" s="3"/>
+      <c r="Z5" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="W5" s="23" t="s">
+      <c r="AA5" s="25" t="s">
         <v>21</v>
       </c>
-      <c r="X5" s="5" t="s">
+      <c r="AB5" s="5" t="s">
         <v>7</v>
       </c>
-      <c r="Y5" s="5" t="s">
+      <c r="AC5" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="Z5" s="3"/>
-      <c r="AA5" s="4" t="s">
-        <v>6</v>
-      </c>
-      <c r="AB5" s="23" t="s">
-        <v>21</v>
-      </c>
-      <c r="AC5" s="5" t="s">
-        <v>7</v>
-      </c>
-      <c r="AD5" s="5" t="s">
-        <v>8</v>
-      </c>
     </row>
     <row x14ac:dyDescent="0.25" r="6" customHeight="1" ht="18.75">
-      <c r="A6" s="11"/>
-      <c r="B6" s="6">
+      <c r="A6" s="6">
         <v>0</v>
       </c>
-      <c r="C6" s="24">
+      <c r="B6" s="26">
         <v>-0.329881</v>
       </c>
+      <c r="C6" s="7">
+        <v>0.931161</v>
+      </c>
       <c r="D6" s="7">
-        <v>0.931161</v>
-      </c>
-      <c r="E6" s="7">
         <v>0.447113</v>
       </c>
-      <c r="F6" s="11"/>
-      <c r="G6" s="6">
+      <c r="E6" s="14"/>
+      <c r="F6" s="6">
         <v>0</v>
       </c>
-      <c r="H6" s="24">
+      <c r="G6" s="26">
         <v>-0.313273</v>
       </c>
+      <c r="H6" s="7">
+        <v>1.07667</v>
+      </c>
       <c r="I6" s="7">
-        <v>1.07667</v>
-      </c>
-      <c r="J6" s="7">
         <v>0.535546</v>
       </c>
-      <c r="K6" s="11"/>
-      <c r="L6" s="6">
+      <c r="J6" s="14"/>
+      <c r="K6" s="6">
         <v>0</v>
       </c>
-      <c r="M6" s="24">
+      <c r="L6" s="26">
         <v>-0.401261</v>
       </c>
+      <c r="M6" s="7">
+        <v>1.09603</v>
+      </c>
       <c r="N6" s="7">
-        <v>1.09603</v>
-      </c>
-      <c r="O6" s="7">
         <v>0.124523</v>
       </c>
-      <c r="P6" s="11"/>
-      <c r="Q6" s="6">
+      <c r="O6" s="14"/>
+      <c r="P6" s="6">
         <v>0</v>
       </c>
-      <c r="R6" s="24">
+      <c r="Q6" s="26">
         <v>-0.178384</v>
       </c>
+      <c r="R6" s="7">
+        <v>0.71111</v>
+      </c>
       <c r="S6" s="7">
-        <v>0.71111</v>
-      </c>
-      <c r="T6" s="7">
         <v>0.37494</v>
       </c>
-      <c r="U6" s="11"/>
-      <c r="V6" s="6">
+      <c r="T6" s="14"/>
+      <c r="U6" s="6">
         <v>0</v>
       </c>
-      <c r="W6" s="24">
+      <c r="V6" s="26">
         <v>-0.177836</v>
       </c>
+      <c r="W6" s="7">
+        <v>0.787593</v>
+      </c>
       <c r="X6" s="7">
-        <v>0.787593</v>
-      </c>
-      <c r="Y6" s="7">
         <v>0.436037</v>
       </c>
-      <c r="Z6" s="11"/>
-      <c r="AA6" s="6">
+      <c r="Y6" s="14"/>
+      <c r="Z6" s="6">
         <v>0</v>
       </c>
-      <c r="AB6" s="24">
+      <c r="AA6" s="26">
         <v>-0.207937</v>
       </c>
+      <c r="AB6" s="7">
+        <v>0.748456</v>
+      </c>
       <c r="AC6" s="7">
-        <v>0.748456</v>
-      </c>
-      <c r="AD6" s="7">
         <v>0.198999</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="7" customHeight="1" ht="18.75">
-      <c r="A7" s="11"/>
-      <c r="B7" s="7">
+      <c r="A7" s="7">
         <v>0.05</v>
       </c>
-      <c r="C7" s="24">
+      <c r="B7" s="26">
         <v>0.755885</v>
       </c>
+      <c r="C7" s="7">
+        <v>-0.278811</v>
+      </c>
       <c r="D7" s="7">
-        <v>-0.278811</v>
-      </c>
-      <c r="E7" s="7">
         <v>-0.540727</v>
       </c>
-      <c r="F7" s="11"/>
-      <c r="G7" s="7">
+      <c r="E7" s="14"/>
+      <c r="F7" s="7">
         <v>0.05</v>
       </c>
-      <c r="H7" s="24">
+      <c r="G7" s="26">
         <v>0.772182</v>
       </c>
+      <c r="H7" s="7">
+        <v>0.41809</v>
+      </c>
       <c r="I7" s="7">
-        <v>0.41809</v>
-      </c>
-      <c r="J7" s="7">
         <v>-1.22785</v>
       </c>
-      <c r="K7" s="11"/>
-      <c r="L7" s="7">
+      <c r="J7" s="14"/>
+      <c r="K7" s="7">
         <v>0.05</v>
       </c>
-      <c r="M7" s="24">
+      <c r="L7" s="26">
         <v>0.510582</v>
       </c>
+      <c r="M7" s="7">
+        <v>0.124945</v>
+      </c>
       <c r="N7" s="7">
-        <v>0.124945</v>
-      </c>
-      <c r="O7" s="7">
         <v>-1.04768</v>
       </c>
-      <c r="P7" s="11"/>
-      <c r="Q7" s="7">
+      <c r="O7" s="14"/>
+      <c r="P7" s="7">
         <v>0.05</v>
       </c>
-      <c r="R7" s="24">
+      <c r="Q7" s="26">
         <v>0.382617</v>
       </c>
+      <c r="R7" s="7">
+        <v>-0.304905</v>
+      </c>
       <c r="S7" s="7">
-        <v>-0.304905</v>
-      </c>
-      <c r="T7" s="7">
         <v>-0.647806</v>
       </c>
-      <c r="U7" s="11"/>
-      <c r="V7" s="7">
+      <c r="T7" s="14"/>
+      <c r="U7" s="7">
         <v>0.05</v>
       </c>
-      <c r="W7" s="24">
+      <c r="V7" s="26">
         <v>0.353577</v>
       </c>
+      <c r="W7" s="7">
+        <v>0.0970245</v>
+      </c>
       <c r="X7" s="7">
-        <v>0.0970245</v>
-      </c>
-      <c r="Y7" s="7">
         <v>-1.10952</v>
       </c>
-      <c r="Z7" s="11"/>
-      <c r="AA7" s="7">
+      <c r="Y7" s="14"/>
+      <c r="Z7" s="7">
         <v>0.05</v>
       </c>
-      <c r="AB7" s="24">
+      <c r="AA7" s="26">
         <v>0.238377</v>
       </c>
+      <c r="AB7" s="7">
+        <v>-0.0989949</v>
+      </c>
       <c r="AC7" s="7">
-        <v>-0.0989949</v>
-      </c>
-      <c r="AD7" s="7">
         <v>-0.899466</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="8" customHeight="1" ht="18.75">
-      <c r="A8" s="11"/>
-      <c r="B8" s="7">
+      <c r="A8" s="7">
         <v>0.1</v>
       </c>
-      <c r="C8" s="24">
+      <c r="B8" s="26">
         <v>1.31579</v>
       </c>
+      <c r="C8" s="7">
+        <v>-0.530977</v>
+      </c>
       <c r="D8" s="7">
-        <v>-0.530977</v>
-      </c>
-      <c r="E8" s="7">
         <v>-0.427211</v>
       </c>
-      <c r="F8" s="11"/>
-      <c r="G8" s="7">
+      <c r="E8" s="14"/>
+      <c r="F8" s="7">
         <v>0.1</v>
       </c>
-      <c r="H8" s="24">
+      <c r="G8" s="26">
         <v>1.31011</v>
       </c>
+      <c r="H8" s="7">
+        <v>0.483361</v>
+      </c>
       <c r="I8" s="7">
-        <v>0.483361</v>
-      </c>
-      <c r="J8" s="7">
         <v>-1.46947</v>
       </c>
-      <c r="K8" s="11"/>
-      <c r="L8" s="7">
+      <c r="J8" s="14"/>
+      <c r="K8" s="7">
         <v>0.1</v>
       </c>
-      <c r="M8" s="24">
+      <c r="L8" s="26">
         <v>0.953244</v>
       </c>
+      <c r="M8" s="7">
+        <v>0.0236556</v>
+      </c>
       <c r="N8" s="7">
-        <v>0.0236556</v>
-      </c>
-      <c r="O8" s="7">
         <v>-1.06892</v>
       </c>
-      <c r="P8" s="11"/>
-      <c r="Q8" s="7">
+      <c r="O8" s="14"/>
+      <c r="P8" s="7">
         <v>0.1</v>
       </c>
-      <c r="R8" s="24">
+      <c r="Q8" s="26">
         <v>0.764056</v>
       </c>
+      <c r="R8" s="7">
+        <v>-0.45438</v>
+      </c>
       <c r="S8" s="7">
-        <v>-0.45438</v>
-      </c>
-      <c r="T8" s="7">
         <v>-0.558891</v>
       </c>
-      <c r="U8" s="11"/>
-      <c r="V8" s="7">
+      <c r="T8" s="14"/>
+      <c r="U8" s="7">
         <v>0.1</v>
       </c>
-      <c r="W8" s="24">
+      <c r="V8" s="26">
         <v>0.70818</v>
       </c>
+      <c r="W8" s="7">
+        <v>0.173366</v>
+      </c>
       <c r="X8" s="7">
-        <v>0.173366</v>
-      </c>
-      <c r="Y8" s="7">
         <v>-1.28281</v>
       </c>
-      <c r="Z8" s="11"/>
-      <c r="AA8" s="7">
+      <c r="Y8" s="14"/>
+      <c r="Z8" s="7">
         <v>0.1</v>
       </c>
-      <c r="AB8" s="24">
+      <c r="AA8" s="26">
         <v>0.533785</v>
       </c>
+      <c r="AB8" s="7">
+        <v>-0.134295</v>
+      </c>
       <c r="AC8" s="7">
-        <v>-0.134295</v>
-      </c>
-      <c r="AD8" s="7">
         <v>-0.939776</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="9" customHeight="1" ht="18.75">
-      <c r="A9" s="11"/>
-      <c r="B9" s="7">
+      <c r="A9" s="7">
         <v>0.15</v>
       </c>
-      <c r="C9" s="24">
+      <c r="B9" s="26">
         <v>1.88832</v>
       </c>
+      <c r="C9" s="7">
+        <v>-0.448544</v>
+      </c>
       <c r="D9" s="7">
-        <v>-0.448544</v>
-      </c>
-      <c r="E9" s="7">
         <v>-0.301523</v>
       </c>
-      <c r="F9" s="11"/>
-      <c r="G9" s="7">
+      <c r="E9" s="14"/>
+      <c r="F9" s="7">
         <v>0.15</v>
       </c>
-      <c r="H9" s="24">
+      <c r="G9" s="26">
         <v>1.84739</v>
       </c>
+      <c r="H9" s="7">
+        <v>0.844665</v>
+      </c>
       <c r="I9" s="7">
-        <v>0.844665</v>
-      </c>
-      <c r="J9" s="7">
         <v>-1.66474</v>
       </c>
-      <c r="K9" s="11"/>
-      <c r="L9" s="7">
+      <c r="J9" s="14"/>
+      <c r="K9" s="7">
         <v>0.15</v>
       </c>
-      <c r="M9" s="24">
+      <c r="L9" s="26">
         <v>1.40889</v>
       </c>
+      <c r="M9" s="7">
+        <v>0.253385</v>
+      </c>
       <c r="N9" s="7">
-        <v>0.253385</v>
-      </c>
-      <c r="O9" s="7">
         <v>-1.13306</v>
       </c>
-      <c r="P9" s="11"/>
-      <c r="Q9" s="7">
+      <c r="O9" s="14"/>
+      <c r="P9" s="7">
         <v>0.15</v>
       </c>
-      <c r="R9" s="24">
+      <c r="Q9" s="26">
         <v>1.18035</v>
       </c>
+      <c r="R9" s="7">
+        <v>-0.37594</v>
+      </c>
       <c r="S9" s="7">
-        <v>-0.37594</v>
-      </c>
-      <c r="T9" s="7">
         <v>-0.432147</v>
       </c>
-      <c r="U9" s="11"/>
-      <c r="V9" s="7">
+      <c r="T9" s="14"/>
+      <c r="U9" s="7">
         <v>0.15</v>
       </c>
-      <c r="W9" s="24">
+      <c r="V9" s="26">
         <v>1.0886</v>
       </c>
+      <c r="W9" s="7">
+        <v>0.480255</v>
+      </c>
       <c r="X9" s="7">
-        <v>0.480255</v>
-      </c>
-      <c r="Y9" s="7">
         <v>-1.43257</v>
       </c>
-      <c r="Z9" s="11"/>
-      <c r="AA9" s="7">
+      <c r="Y9" s="14"/>
+      <c r="Z9" s="7">
         <v>0.15</v>
       </c>
-      <c r="AB9" s="24">
+      <c r="AA9" s="26">
         <v>0.855006</v>
       </c>
+      <c r="AB9" s="7">
+        <v>0.0586839</v>
+      </c>
       <c r="AC9" s="7">
-        <v>0.0586839</v>
-      </c>
-      <c r="AD9" s="7">
         <v>-0.988256</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="10" customHeight="1" ht="18.75">
-      <c r="A10" s="11"/>
-      <c r="B10" s="7">
+      <c r="A10" s="7">
         <v>0.2</v>
       </c>
-      <c r="C10" s="24">
+      <c r="B10" s="26">
         <v>2.27727</v>
       </c>
+      <c r="C10" s="7">
+        <v>-0.224848</v>
+      </c>
       <c r="D10" s="7">
-        <v>-0.224848</v>
-      </c>
-      <c r="E10" s="7">
         <v>-0.209021</v>
       </c>
-      <c r="F10" s="11"/>
-      <c r="G10" s="7">
+      <c r="E10" s="14"/>
+      <c r="F10" s="7">
         <v>0.2</v>
       </c>
-      <c r="H10" s="24">
+      <c r="G10" s="26">
         <v>2.2065</v>
       </c>
+      <c r="H10" s="7">
+        <v>1.23544</v>
+      </c>
       <c r="I10" s="7">
-        <v>1.23544</v>
-      </c>
-      <c r="J10" s="7">
         <v>-1.77688</v>
       </c>
-      <c r="K10" s="11"/>
-      <c r="L10" s="7">
+      <c r="J10" s="14"/>
+      <c r="K10" s="7">
         <v>0.2</v>
       </c>
-      <c r="M10" s="24">
+      <c r="L10" s="26">
         <v>1.71845</v>
       </c>
+      <c r="M10" s="7">
+        <v>0.572429</v>
+      </c>
       <c r="N10" s="7">
-        <v>0.572429</v>
-      </c>
-      <c r="O10" s="7">
         <v>-1.19448</v>
       </c>
-      <c r="P10" s="11"/>
-      <c r="Q10" s="7">
+      <c r="O10" s="14"/>
+      <c r="P10" s="7">
         <v>0.2</v>
       </c>
-      <c r="R10" s="24">
+      <c r="Q10" s="26">
         <v>1.47458</v>
       </c>
+      <c r="R10" s="7">
+        <v>-0.19867</v>
+      </c>
       <c r="S10" s="7">
-        <v>-0.19867</v>
-      </c>
-      <c r="T10" s="7">
         <v>-0.327142</v>
       </c>
-      <c r="U10" s="11"/>
-      <c r="V10" s="7">
+      <c r="T10" s="14"/>
+      <c r="U10" s="7">
         <v>0.2</v>
       </c>
-      <c r="W10" s="24">
+      <c r="V10" s="26">
         <v>1.35351</v>
       </c>
+      <c r="W10" s="7">
+        <v>0.807865</v>
+      </c>
       <c r="X10" s="7">
-        <v>0.807865</v>
-      </c>
-      <c r="Y10" s="7">
         <v>-1.52186</v>
       </c>
-      <c r="Z10" s="11"/>
-      <c r="AA10" s="7">
+      <c r="Y10" s="14"/>
+      <c r="Z10" s="7">
         <v>0.2</v>
       </c>
-      <c r="AB10" s="24">
+      <c r="AA10" s="26">
         <v>1.08082</v>
       </c>
+      <c r="AB10" s="7">
+        <v>0.310345</v>
+      </c>
       <c r="AC10" s="7">
-        <v>0.310345</v>
-      </c>
-      <c r="AD10" s="7">
         <v>-1.02524</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="11" customHeight="1" ht="18.75">
-      <c r="A11" s="11"/>
-      <c r="B11" s="7">
+      <c r="A11" s="7">
         <v>0.25</v>
       </c>
-      <c r="C11" s="24">
+      <c r="B11" s="26">
         <v>2.88633</v>
       </c>
+      <c r="C11" s="7">
+        <v>0.301023</v>
+      </c>
       <c r="D11" s="7">
-        <v>0.301023</v>
-      </c>
-      <c r="E11" s="7">
         <v>-0.0670585</v>
       </c>
-      <c r="F11" s="11"/>
-      <c r="G11" s="7">
+      <c r="E11" s="14"/>
+      <c r="F11" s="7">
         <v>0.25</v>
       </c>
-      <c r="H11" s="24">
+      <c r="G11" s="26">
         <v>2.7617</v>
       </c>
+      <c r="H11" s="7">
+        <v>1.99211</v>
+      </c>
       <c r="I11" s="7">
-        <v>1.99211</v>
-      </c>
-      <c r="J11" s="7">
         <v>-1.93728</v>
       </c>
-      <c r="K11" s="11"/>
-      <c r="L11" s="7">
+      <c r="J11" s="14"/>
+      <c r="K11" s="7">
         <v>0.25</v>
       </c>
-      <c r="M11" s="24">
+      <c r="L11" s="26">
         <v>2.20346</v>
       </c>
+      <c r="M11" s="7">
+        <v>1.23542</v>
+      </c>
       <c r="N11" s="7">
-        <v>1.23542</v>
-      </c>
-      <c r="O11" s="7">
         <v>-1.30952</v>
       </c>
-      <c r="P11" s="11"/>
-      <c r="Q11" s="7">
+      <c r="O11" s="14"/>
+      <c r="P11" s="7">
         <v>0.25</v>
       </c>
-      <c r="R11" s="24">
+      <c r="Q11" s="26">
         <v>1.95028</v>
       </c>
+      <c r="R11" s="7">
+        <v>0.220674</v>
+      </c>
       <c r="S11" s="7">
-        <v>0.220674</v>
-      </c>
-      <c r="T11" s="7">
         <v>-0.153192</v>
       </c>
-      <c r="U11" s="11"/>
-      <c r="V11" s="7">
+      <c r="T11" s="14"/>
+      <c r="U11" s="7">
         <v>0.25</v>
       </c>
-      <c r="W11" s="24">
+      <c r="V11" s="26">
         <v>1.77715</v>
       </c>
+      <c r="W11" s="7">
+        <v>1.44581</v>
+      </c>
       <c r="X11" s="7">
-        <v>1.44581</v>
-      </c>
-      <c r="Y11" s="7">
         <v>-1.65089</v>
       </c>
-      <c r="Z11" s="11"/>
-      <c r="AA11" s="7">
+      <c r="Y11" s="14"/>
+      <c r="Z11" s="7">
         <v>0.25</v>
       </c>
-      <c r="AB11" s="24">
+      <c r="AA11" s="26">
         <v>1.44734</v>
       </c>
+      <c r="AB11" s="7">
+        <v>0.835472</v>
+      </c>
       <c r="AC11" s="7">
-        <v>0.835472</v>
-      </c>
-      <c r="AD11" s="7">
         <v>-1.08968</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="12" customHeight="1" ht="18.75">
-      <c r="A12" s="11"/>
-      <c r="B12" s="7">
+      <c r="A12" s="7">
         <v>0.30198</v>
       </c>
-      <c r="C12" s="24">
+      <c r="B12" s="26">
         <v>3.34133</v>
       </c>
+      <c r="C12" s="7">
+        <v>0.764369</v>
+      </c>
       <c r="D12" s="7">
-        <v>0.764369</v>
-      </c>
-      <c r="E12" s="7">
         <v>0.0312122</v>
       </c>
-      <c r="F12" s="11"/>
-      <c r="G12" s="7">
+      <c r="E12" s="14"/>
+      <c r="F12" s="7">
         <v>0.30198</v>
       </c>
-      <c r="H12" s="24">
+      <c r="G12" s="26">
         <v>3.17102</v>
       </c>
+      <c r="H12" s="7">
+        <v>2.60576</v>
+      </c>
       <c r="I12" s="7">
-        <v>2.60576</v>
-      </c>
-      <c r="J12" s="7">
         <v>-2.05821</v>
       </c>
-      <c r="K12" s="11"/>
-      <c r="L12" s="7">
+      <c r="J12" s="14"/>
+      <c r="K12" s="7">
         <v>0.30198</v>
       </c>
-      <c r="M12" s="24">
+      <c r="L12" s="26">
         <v>2.56677</v>
       </c>
+      <c r="M12" s="7">
+        <v>1.79006</v>
+      </c>
       <c r="N12" s="7">
-        <v>1.79006</v>
-      </c>
-      <c r="O12" s="7">
         <v>-1.40999</v>
       </c>
-      <c r="P12" s="11"/>
-      <c r="Q12" s="7">
+      <c r="O12" s="14"/>
+      <c r="P12" s="7">
         <v>0.30198</v>
       </c>
-      <c r="R12" s="24">
+      <c r="Q12" s="26">
         <v>2.31242</v>
       </c>
+      <c r="R12" s="7">
+        <v>0.58995</v>
+      </c>
       <c r="S12" s="7">
-        <v>0.58995</v>
-      </c>
-      <c r="T12" s="7">
         <v>-0.0243899</v>
       </c>
-      <c r="U12" s="11"/>
-      <c r="V12" s="7">
+      <c r="T12" s="14"/>
+      <c r="U12" s="7">
         <v>0.30198</v>
       </c>
-      <c r="W12" s="24">
+      <c r="V12" s="26">
         <v>2.0962</v>
       </c>
+      <c r="W12" s="7">
+        <v>1.96166</v>
+      </c>
       <c r="X12" s="7">
-        <v>1.96166</v>
-      </c>
-      <c r="Y12" s="7">
         <v>-1.74827</v>
       </c>
-      <c r="Z12" s="11"/>
-      <c r="AA12" s="7">
+      <c r="Y12" s="14"/>
+      <c r="Z12" s="7">
         <v>0.30198</v>
       </c>
-      <c r="AB12" s="24">
+      <c r="AA12" s="26">
         <v>1.72812</v>
       </c>
+      <c r="AB12" s="7">
+        <v>1.27343</v>
+      </c>
       <c r="AC12" s="7">
-        <v>1.27343</v>
-      </c>
-      <c r="AD12" s="7">
         <v>-1.14501</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="13" customHeight="1" ht="18.75">
-      <c r="A13" s="11"/>
-      <c r="B13" s="7">
+      <c r="A13" s="7">
         <v>0.35365</v>
       </c>
-      <c r="C13" s="24">
+      <c r="B13" s="26">
         <v>3.81344</v>
       </c>
+      <c r="C13" s="7">
+        <v>1.27333</v>
+      </c>
       <c r="D13" s="7">
-        <v>1.27333</v>
-      </c>
-      <c r="E13" s="7">
         <v>0.122242</v>
       </c>
-      <c r="F13" s="11"/>
-      <c r="G13" s="7">
+      <c r="E13" s="14"/>
+      <c r="F13" s="7">
         <v>0.35365</v>
       </c>
-      <c r="H13" s="24">
+      <c r="G13" s="26">
         <v>3.58947</v>
       </c>
+      <c r="H13" s="7">
+        <v>3.26045</v>
+      </c>
       <c r="I13" s="7">
-        <v>3.26045</v>
-      </c>
-      <c r="J13" s="7">
         <v>-2.19769</v>
       </c>
-      <c r="K13" s="11"/>
-      <c r="L13" s="7">
+      <c r="J13" s="14"/>
+      <c r="K13" s="7">
         <v>0.35365</v>
       </c>
-      <c r="M13" s="24">
+      <c r="L13" s="26">
         <v>2.94073</v>
       </c>
+      <c r="M13" s="7">
+        <v>2.38717</v>
+      </c>
       <c r="N13" s="7">
-        <v>2.38717</v>
-      </c>
-      <c r="O13" s="7">
         <v>-1.53075</v>
       </c>
-      <c r="P13" s="11"/>
-      <c r="Q13" s="7">
+      <c r="O13" s="14"/>
+      <c r="P13" s="7">
         <v>0.35365</v>
       </c>
-      <c r="R13" s="24">
+      <c r="Q13" s="26">
         <v>2.6893</v>
       </c>
+      <c r="R13" s="7">
+        <v>0.994612</v>
+      </c>
       <c r="S13" s="7">
-        <v>0.994612</v>
-      </c>
-      <c r="T13" s="7">
         <v>0.103184</v>
       </c>
-      <c r="U13" s="11"/>
-      <c r="V13" s="7">
+      <c r="T13" s="14"/>
+      <c r="U13" s="7">
         <v>0.35365</v>
       </c>
-      <c r="W13" s="24">
+      <c r="V13" s="26">
         <v>2.42357</v>
       </c>
+      <c r="W13" s="7">
+        <v>2.50979</v>
+      </c>
       <c r="X13" s="7">
-        <v>2.50979</v>
-      </c>
-      <c r="Y13" s="7">
         <v>-1.86022</v>
       </c>
-      <c r="Z13" s="11"/>
-      <c r="AA13" s="7">
+      <c r="Y13" s="14"/>
+      <c r="Z13" s="7">
         <v>0.35365</v>
       </c>
-      <c r="AB13" s="24">
+      <c r="AA13" s="26">
         <v>2.01826</v>
       </c>
+      <c r="AB13" s="7">
+        <v>1.74315</v>
+      </c>
       <c r="AC13" s="7">
-        <v>1.74315</v>
-      </c>
-      <c r="AD13" s="7">
         <v>-1.21334</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="14" customHeight="1" ht="18.75">
-      <c r="A14" s="11"/>
-      <c r="B14" s="7">
+      <c r="A14" s="7">
         <v>0.40358</v>
       </c>
-      <c r="C14" s="24">
+      <c r="B14" s="26">
         <v>4.22105</v>
       </c>
+      <c r="C14" s="7">
+        <v>1.72966</v>
+      </c>
       <c r="D14" s="7">
-        <v>1.72966</v>
-      </c>
-      <c r="E14" s="7">
         <v>0.192892</v>
       </c>
-      <c r="F14" s="11"/>
-      <c r="G14" s="7">
+      <c r="E14" s="14"/>
+      <c r="F14" s="7">
         <v>0.40358</v>
       </c>
-      <c r="H14" s="24">
+      <c r="G14" s="26">
         <v>3.94592</v>
       </c>
+      <c r="H14" s="7">
+        <v>3.83365</v>
+      </c>
       <c r="I14" s="7">
-        <v>3.83365</v>
-      </c>
-      <c r="J14" s="7">
         <v>-2.3279</v>
       </c>
-      <c r="K14" s="11"/>
-      <c r="L14" s="7">
+      <c r="J14" s="14"/>
+      <c r="K14" s="7">
         <v>0.40358</v>
       </c>
-      <c r="M14" s="24">
+      <c r="L14" s="26">
         <v>3.26142</v>
       </c>
+      <c r="M14" s="7">
+        <v>2.91371</v>
+      </c>
       <c r="N14" s="7">
-        <v>2.91371</v>
-      </c>
-      <c r="O14" s="7">
         <v>-1.64668</v>
       </c>
-      <c r="P14" s="11"/>
-      <c r="Q14" s="7">
+      <c r="O14" s="14"/>
+      <c r="P14" s="7">
         <v>0.40358</v>
       </c>
-      <c r="R14" s="24">
+      <c r="Q14" s="26">
         <v>3.01531</v>
       </c>
+      <c r="R14" s="7">
+        <v>1.35627</v>
+      </c>
       <c r="S14" s="7">
-        <v>1.35627</v>
-      </c>
-      <c r="T14" s="7">
         <v>0.208549</v>
       </c>
-      <c r="U14" s="11"/>
-      <c r="V14" s="7">
+      <c r="T14" s="14"/>
+      <c r="U14" s="7">
         <v>0.40358</v>
       </c>
-      <c r="W14" s="24">
+      <c r="V14" s="26">
         <v>2.70344</v>
       </c>
+      <c r="W14" s="7">
+        <v>2.98654</v>
+      </c>
       <c r="X14" s="7">
-        <v>2.98654</v>
-      </c>
-      <c r="Y14" s="7">
         <v>-1.9633</v>
       </c>
-      <c r="Z14" s="11"/>
-      <c r="AA14" s="7">
+      <c r="Y14" s="14"/>
+      <c r="Z14" s="7">
         <v>0.40358</v>
       </c>
-      <c r="AB14" s="24">
+      <c r="AA14" s="26">
         <v>2.26832</v>
       </c>
+      <c r="AB14" s="7">
+        <v>2.15502</v>
+      </c>
       <c r="AC14" s="7">
-        <v>2.15502</v>
-      </c>
-      <c r="AD14" s="7">
         <v>-1.27936</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="15" customHeight="1" ht="18.75">
-      <c r="A15" s="11"/>
-      <c r="B15" s="7">
+      <c r="A15" s="7">
         <v>0.45421</v>
       </c>
-      <c r="C15" s="24">
+      <c r="B15" s="26">
         <v>4.64308</v>
       </c>
+      <c r="C15" s="7">
+        <v>2.24416</v>
+      </c>
       <c r="D15" s="7">
-        <v>2.24416</v>
-      </c>
-      <c r="E15" s="7">
         <v>0.267669</v>
       </c>
-      <c r="F15" s="11"/>
-      <c r="G15" s="7">
+      <c r="E15" s="14"/>
+      <c r="F15" s="7">
         <v>0.45421</v>
       </c>
-      <c r="H15" s="24">
+      <c r="G15" s="26">
         <v>4.309</v>
       </c>
+      <c r="H15" s="7">
+        <v>4.45749</v>
+      </c>
       <c r="I15" s="7">
-        <v>4.45749</v>
-      </c>
-      <c r="J15" s="7">
         <v>-2.46915</v>
       </c>
-      <c r="K15" s="11"/>
-      <c r="L15" s="7">
+      <c r="J15" s="14"/>
+      <c r="K15" s="7">
         <v>0.45421</v>
       </c>
-      <c r="M15" s="24">
+      <c r="L15" s="26">
         <v>3.59093</v>
       </c>
+      <c r="M15" s="7">
+        <v>3.49446</v>
+      </c>
       <c r="N15" s="7">
-        <v>3.49446</v>
-      </c>
-      <c r="O15" s="7">
         <v>-1.77754</v>
       </c>
-      <c r="P15" s="11"/>
-      <c r="Q15" s="7">
+      <c r="O15" s="14"/>
+      <c r="P15" s="7">
         <v>0.45421</v>
       </c>
-      <c r="R15" s="24">
+      <c r="Q15" s="26">
         <v>3.34873</v>
       </c>
+      <c r="R15" s="7">
+        <v>1.76556</v>
+      </c>
       <c r="S15" s="7">
-        <v>1.76556</v>
-      </c>
-      <c r="T15" s="7">
         <v>0.322329</v>
       </c>
-      <c r="U15" s="11"/>
-      <c r="V15" s="7">
+      <c r="T15" s="14"/>
+      <c r="U15" s="7">
         <v>0.45421</v>
       </c>
-      <c r="W15" s="24">
+      <c r="V15" s="26">
         <v>2.98637</v>
       </c>
+      <c r="W15" s="7">
+        <v>3.49901</v>
+      </c>
       <c r="X15" s="7">
-        <v>3.49901</v>
-      </c>
-      <c r="Y15" s="7">
         <v>-2.0693</v>
       </c>
-      <c r="Z15" s="11"/>
-      <c r="AA15" s="7">
+      <c r="Y15" s="14"/>
+      <c r="Z15" s="7">
         <v>0.45421</v>
       </c>
-      <c r="AB15" s="24">
+      <c r="AA15" s="26">
         <v>2.52378</v>
       </c>
+      <c r="AB15" s="7">
+        <v>2.60642</v>
+      </c>
       <c r="AC15" s="7">
-        <v>2.60642</v>
-      </c>
-      <c r="AD15" s="7">
         <v>-1.35143</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="16" customHeight="1" ht="18.75">
-      <c r="A16" s="11"/>
-      <c r="B16" s="7">
+      <c r="A16" s="7">
         <v>0.50322</v>
       </c>
-      <c r="C16" s="24">
+      <c r="B16" s="26">
         <v>4.96865</v>
       </c>
+      <c r="C16" s="7">
+        <v>2.65912</v>
+      </c>
       <c r="D16" s="7">
-        <v>2.65912</v>
-      </c>
-      <c r="E16" s="7">
         <v>0.334106</v>
       </c>
-      <c r="F16" s="11"/>
-      <c r="G16" s="7">
+      <c r="E16" s="14"/>
+      <c r="F16" s="7">
         <v>0.50322</v>
       </c>
-      <c r="H16" s="24">
+      <c r="G16" s="26">
         <v>4.58305</v>
       </c>
+      <c r="H16" s="7">
+        <v>4.95779</v>
+      </c>
       <c r="I16" s="7">
-        <v>4.95779</v>
-      </c>
-      <c r="J16" s="7">
         <v>-2.579</v>
       </c>
-      <c r="K16" s="11"/>
-      <c r="L16" s="7">
+      <c r="J16" s="14"/>
+      <c r="K16" s="7">
         <v>0.50322</v>
       </c>
-      <c r="M16" s="24">
+      <c r="L16" s="26">
         <v>3.83757</v>
       </c>
+      <c r="M16" s="7">
+        <v>3.96005</v>
+      </c>
       <c r="N16" s="7">
-        <v>3.96005</v>
-      </c>
-      <c r="O16" s="7">
         <v>-1.8809</v>
       </c>
-      <c r="P16" s="11"/>
-      <c r="Q16" s="7">
+      <c r="O16" s="14"/>
+      <c r="P16" s="7">
         <v>0.50322</v>
       </c>
-      <c r="R16" s="24">
+      <c r="Q16" s="26">
         <v>3.60021</v>
       </c>
+      <c r="R16" s="7">
+        <v>2.09124</v>
+      </c>
       <c r="S16" s="7">
-        <v>2.09124</v>
-      </c>
-      <c r="T16" s="7">
         <v>0.418984</v>
       </c>
-      <c r="U16" s="11"/>
-      <c r="V16" s="7">
+      <c r="T16" s="14"/>
+      <c r="U16" s="7">
         <v>0.50322</v>
       </c>
-      <c r="W16" s="24">
+      <c r="V16" s="26">
         <v>3.19641</v>
       </c>
+      <c r="W16" s="7">
+        <v>3.90032</v>
+      </c>
       <c r="X16" s="7">
-        <v>3.90032</v>
-      </c>
-      <c r="Y16" s="7">
         <v>-2.14378</v>
       </c>
-      <c r="Z16" s="11"/>
-      <c r="AA16" s="7">
+      <c r="Y16" s="14"/>
+      <c r="Z16" s="7">
         <v>0.50322</v>
       </c>
-      <c r="AB16" s="24">
+      <c r="AA16" s="26">
         <v>2.71302</v>
       </c>
+      <c r="AB16" s="7">
+        <v>2.96105</v>
+      </c>
       <c r="AC16" s="7">
-        <v>2.96105</v>
-      </c>
-      <c r="AD16" s="7">
         <v>-1.40229</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="17" customHeight="1" ht="18.75">
-      <c r="A17" s="11"/>
-      <c r="B17" s="7">
+      <c r="A17" s="7">
         <v>0.55384</v>
       </c>
-      <c r="C17" s="24">
+      <c r="B17" s="26">
         <v>5.13679</v>
       </c>
+      <c r="C17" s="7">
+        <v>2.8649</v>
+      </c>
       <c r="D17" s="7">
-        <v>2.8649</v>
-      </c>
-      <c r="E17" s="7">
         <v>0.372259</v>
       </c>
-      <c r="F17" s="11"/>
-      <c r="G17" s="7">
+      <c r="E17" s="14"/>
+      <c r="F17" s="7">
         <v>0.55384</v>
       </c>
-      <c r="H17" s="24">
+      <c r="G17" s="26">
         <v>4.72202</v>
       </c>
+      <c r="H17" s="7">
+        <v>5.20835</v>
+      </c>
       <c r="I17" s="7">
-        <v>5.20835</v>
-      </c>
-      <c r="J17" s="7">
         <v>-2.6363</v>
       </c>
-      <c r="K17" s="11"/>
-      <c r="L17" s="7">
+      <c r="J17" s="14"/>
+      <c r="K17" s="7">
         <v>0.55384</v>
       </c>
-      <c r="M17" s="24">
+      <c r="L17" s="26">
         <v>3.96254</v>
       </c>
+      <c r="M17" s="7">
+        <v>4.19158</v>
+      </c>
       <c r="N17" s="7">
-        <v>4.19158</v>
-      </c>
-      <c r="O17" s="7">
         <v>-1.93224</v>
       </c>
-      <c r="P17" s="11"/>
-      <c r="Q17" s="7">
+      <c r="O17" s="14"/>
+      <c r="P17" s="7">
         <v>0.55384</v>
       </c>
-      <c r="R17" s="24">
+      <c r="Q17" s="26">
         <v>3.72672</v>
       </c>
+      <c r="R17" s="7">
+        <v>2.2504</v>
+      </c>
       <c r="S17" s="7">
-        <v>2.2504</v>
-      </c>
-      <c r="T17" s="7">
         <v>0.471651</v>
       </c>
-      <c r="U17" s="11"/>
-      <c r="V17" s="7">
+      <c r="T17" s="14"/>
+      <c r="U17" s="7">
         <v>0.55384</v>
       </c>
-      <c r="W17" s="24">
+      <c r="V17" s="26">
         <v>3.30098</v>
       </c>
+      <c r="W17" s="7">
+        <v>4.09619</v>
+      </c>
       <c r="X17" s="7">
-        <v>4.09619</v>
-      </c>
-      <c r="Y17" s="7">
         <v>-2.17911</v>
       </c>
-      <c r="Z17" s="11"/>
-      <c r="AA17" s="7">
+      <c r="Y17" s="14"/>
+      <c r="Z17" s="7">
         <v>0.55384</v>
       </c>
-      <c r="AB17" s="24">
+      <c r="AA17" s="26">
         <v>2.80753</v>
       </c>
+      <c r="AB17" s="7">
+        <v>3.13369</v>
+      </c>
       <c r="AC17" s="7">
-        <v>3.13369</v>
-      </c>
-      <c r="AD17" s="7">
         <v>-1.42468</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="18" customHeight="1" ht="18.75">
-      <c r="A18" s="11"/>
-      <c r="B18" s="7">
+      <c r="A18" s="7">
         <v>0.60384</v>
       </c>
-      <c r="C18" s="24">
+      <c r="B18" s="26">
         <v>5.34457</v>
       </c>
+      <c r="C18" s="7">
+        <v>3.10654</v>
+      </c>
       <c r="D18" s="7">
-        <v>3.10654</v>
-      </c>
-      <c r="E18" s="7">
         <v>0.42197</v>
       </c>
-      <c r="F18" s="11"/>
-      <c r="G18" s="7">
+      <c r="E18" s="14"/>
+      <c r="F18" s="7">
         <v>0.60384</v>
       </c>
-      <c r="H18" s="24">
+      <c r="G18" s="26">
         <v>4.89398</v>
       </c>
+      <c r="H18" s="7">
+        <v>5.49749</v>
+      </c>
       <c r="I18" s="7">
-        <v>5.49749</v>
-      </c>
-      <c r="J18" s="7">
         <v>-2.70141</v>
       </c>
-      <c r="K18" s="11"/>
-      <c r="L18" s="7">
+      <c r="J18" s="14"/>
+      <c r="K18" s="7">
         <v>0.60384</v>
       </c>
-      <c r="M18" s="24">
+      <c r="L18" s="26">
         <v>4.12091</v>
       </c>
+      <c r="M18" s="7">
+        <v>4.4604</v>
+      </c>
       <c r="N18" s="7">
-        <v>4.4604</v>
-      </c>
-      <c r="O18" s="7">
         <v>-1.98761</v>
       </c>
-      <c r="P18" s="11"/>
-      <c r="Q18" s="7">
+      <c r="O18" s="14"/>
+      <c r="P18" s="7">
         <v>0.60384</v>
       </c>
-      <c r="R18" s="24">
+      <c r="Q18" s="26">
         <v>3.8818</v>
       </c>
+      <c r="R18" s="7">
+        <v>2.43812</v>
+      </c>
       <c r="S18" s="7">
-        <v>2.43812</v>
-      </c>
-      <c r="T18" s="7">
         <v>0.536306</v>
       </c>
-      <c r="U18" s="11"/>
-      <c r="V18" s="7">
+      <c r="T18" s="14"/>
+      <c r="U18" s="7">
         <v>0.60384</v>
       </c>
-      <c r="W18" s="24">
+      <c r="V18" s="26">
         <v>3.43136</v>
       </c>
+      <c r="W18" s="7">
+        <v>4.31769</v>
+      </c>
       <c r="X18" s="7">
-        <v>4.31769</v>
-      </c>
-      <c r="Y18" s="7">
         <v>-2.21477</v>
       </c>
-      <c r="Z18" s="11"/>
-      <c r="AA18" s="7">
+      <c r="Y18" s="14"/>
+      <c r="Z18" s="7">
         <v>0.60384</v>
       </c>
-      <c r="AB18" s="24">
+      <c r="AA18" s="26">
         <v>2.92864</v>
       </c>
+      <c r="AB18" s="7">
+        <v>3.33271</v>
+      </c>
       <c r="AC18" s="7">
-        <v>3.33271</v>
-      </c>
-      <c r="AD18" s="7">
         <v>-1.44481</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="19" customHeight="1" ht="18.75">
-      <c r="A19" s="11"/>
-      <c r="B19" s="7">
+      <c r="A19" s="7">
         <v>0.65565</v>
       </c>
-      <c r="C19" s="24">
+      <c r="B19" s="26">
         <v>5.55129</v>
       </c>
+      <c r="C19" s="7">
+        <v>3.33599</v>
+      </c>
       <c r="D19" s="7">
-        <v>3.33599</v>
-      </c>
-      <c r="E19" s="7">
         <v>0.470988</v>
       </c>
-      <c r="F19" s="11"/>
-      <c r="G19" s="7">
+      <c r="E19" s="14"/>
+      <c r="F19" s="7">
         <v>0.65565</v>
       </c>
-      <c r="H19" s="24">
+      <c r="G19" s="26">
         <v>5.06333</v>
       </c>
+      <c r="H19" s="7">
+        <v>5.77392</v>
+      </c>
       <c r="I19" s="7">
-        <v>5.77392</v>
-      </c>
-      <c r="J19" s="7">
         <v>-2.76799</v>
       </c>
-      <c r="K19" s="11"/>
-      <c r="L19" s="7">
+      <c r="J19" s="14"/>
+      <c r="K19" s="7">
         <v>0.65565</v>
       </c>
-      <c r="M19" s="24">
+      <c r="L19" s="26">
         <v>4.27762</v>
       </c>
+      <c r="M19" s="7">
+        <v>4.71587</v>
+      </c>
       <c r="N19" s="7">
-        <v>4.71587</v>
-      </c>
-      <c r="O19" s="7">
         <v>-2.0408</v>
       </c>
-      <c r="P19" s="11"/>
-      <c r="Q19" s="7">
+      <c r="O19" s="14"/>
+      <c r="P19" s="7">
         <v>0.65565</v>
       </c>
-      <c r="R19" s="24">
+      <c r="Q19" s="26">
         <v>4.03481</v>
       </c>
+      <c r="R19" s="7">
+        <v>2.61607</v>
+      </c>
       <c r="S19" s="7">
-        <v>2.61607</v>
-      </c>
-      <c r="T19" s="7">
         <v>0.600154</v>
       </c>
-      <c r="U19" s="11"/>
-      <c r="V19" s="7">
+      <c r="T19" s="14"/>
+      <c r="U19" s="7">
         <v>0.65565</v>
       </c>
-      <c r="W19" s="24">
+      <c r="V19" s="26">
         <v>3.55927</v>
       </c>
+      <c r="W19" s="7">
+        <v>4.52811</v>
+      </c>
       <c r="X19" s="7">
-        <v>4.52811</v>
-      </c>
-      <c r="Y19" s="7">
         <v>-2.25038</v>
       </c>
-      <c r="Z19" s="11"/>
-      <c r="AA19" s="7">
+      <c r="Y19" s="14"/>
+      <c r="Z19" s="7">
         <v>0.65565</v>
       </c>
-      <c r="AB19" s="24">
+      <c r="AA19" s="26">
         <v>3.04794</v>
       </c>
+      <c r="AB19" s="7">
+        <v>3.52128</v>
+      </c>
       <c r="AC19" s="7">
-        <v>3.52128</v>
-      </c>
-      <c r="AD19" s="7">
         <v>-1.46303</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="20" customHeight="1" ht="18.75">
-      <c r="A20" s="11"/>
-      <c r="B20" s="7">
+      <c r="A20" s="7">
         <v>0.70225</v>
       </c>
-      <c r="C20" s="24">
+      <c r="B20" s="26">
         <v>5.71674</v>
       </c>
+      <c r="C20" s="7">
+        <v>3.52185</v>
+      </c>
       <c r="D20" s="7">
-        <v>3.52185</v>
-      </c>
-      <c r="E20" s="7">
         <v>0.51087</v>
       </c>
-      <c r="F20" s="11"/>
-      <c r="G20" s="7">
+      <c r="E20" s="14"/>
+      <c r="F20" s="7">
         <v>0.70225</v>
       </c>
-      <c r="H20" s="24">
+      <c r="G20" s="26">
         <v>5.19779</v>
       </c>
+      <c r="H20" s="7">
+        <v>5.99596</v>
+      </c>
       <c r="I20" s="7">
-        <v>5.99596</v>
-      </c>
-      <c r="J20" s="7">
         <v>-2.82134</v>
       </c>
-      <c r="K20" s="11"/>
-      <c r="L20" s="7">
+      <c r="J20" s="14"/>
+      <c r="K20" s="7">
         <v>0.70225</v>
       </c>
-      <c r="M20" s="24">
+      <c r="L20" s="26">
         <v>4.40254</v>
       </c>
+      <c r="M20" s="7">
+        <v>4.92149</v>
+      </c>
       <c r="N20" s="7">
-        <v>4.92149</v>
-      </c>
-      <c r="O20" s="7">
         <v>-2.0829</v>
       </c>
-      <c r="P20" s="11"/>
-      <c r="Q20" s="7">
+      <c r="O20" s="14"/>
+      <c r="P20" s="7">
         <v>0.70225</v>
       </c>
-      <c r="R20" s="24">
+      <c r="Q20" s="26">
         <v>4.15674</v>
       </c>
+      <c r="R20" s="7">
+        <v>2.76113</v>
+      </c>
       <c r="S20" s="7">
-        <v>2.76113</v>
-      </c>
-      <c r="T20" s="7">
         <v>0.65251</v>
       </c>
-      <c r="U20" s="11"/>
-      <c r="V20" s="7">
+      <c r="T20" s="14"/>
+      <c r="U20" s="7">
         <v>0.70225</v>
       </c>
-      <c r="W20" s="24">
+      <c r="V20" s="26">
         <v>3.6608</v>
       </c>
+      <c r="W20" s="7">
+        <v>4.69749</v>
+      </c>
       <c r="X20" s="7">
-        <v>4.69749</v>
-      </c>
-      <c r="Y20" s="7">
         <v>-2.27762</v>
       </c>
-      <c r="Z20" s="11"/>
-      <c r="AA20" s="7">
+      <c r="Y20" s="14"/>
+      <c r="Z20" s="7">
         <v>0.70225</v>
       </c>
-      <c r="AB20" s="24">
+      <c r="AA20" s="26">
         <v>3.14293</v>
       </c>
+      <c r="AB20" s="7">
+        <v>3.67379</v>
+      </c>
       <c r="AC20" s="7">
-        <v>3.67379</v>
-      </c>
-      <c r="AD20" s="7">
         <v>-1.4765</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="21" customHeight="1" ht="18.75">
-      <c r="A21" s="11"/>
-      <c r="B21" s="7">
+      <c r="A21" s="7">
         <v>0.75206</v>
       </c>
-      <c r="C21" s="24">
+      <c r="B21" s="26">
         <v>5.93007</v>
       </c>
+      <c r="C21" s="7">
+        <v>3.77298</v>
+      </c>
       <c r="D21" s="7">
-        <v>3.77298</v>
-      </c>
-      <c r="E21" s="7">
         <v>0.564015</v>
       </c>
-      <c r="F21" s="11"/>
-      <c r="G21" s="7">
+      <c r="E21" s="14"/>
+      <c r="F21" s="7">
         <v>0.75206</v>
       </c>
-      <c r="H21" s="24">
+      <c r="G21" s="26">
         <v>5.3693</v>
       </c>
+      <c r="H21" s="7">
+        <v>6.29155</v>
+      </c>
       <c r="I21" s="7">
-        <v>6.29155</v>
-      </c>
-      <c r="J21" s="7">
         <v>-2.89084</v>
       </c>
-      <c r="K21" s="11"/>
-      <c r="L21" s="7">
+      <c r="J21" s="14"/>
+      <c r="K21" s="7">
         <v>0.75206</v>
       </c>
-      <c r="M21" s="24">
+      <c r="L21" s="26">
         <v>4.56253</v>
       </c>
+      <c r="M21" s="7">
+        <v>5.19664</v>
+      </c>
       <c r="N21" s="7">
-        <v>5.19664</v>
-      </c>
-      <c r="O21" s="7">
         <v>-2.1377</v>
       </c>
-      <c r="P21" s="11"/>
-      <c r="Q21" s="7">
+      <c r="O21" s="14"/>
+      <c r="P21" s="7">
         <v>0.75206</v>
       </c>
-      <c r="R21" s="24">
+      <c r="Q21" s="26">
         <v>4.31275</v>
       </c>
+      <c r="R21" s="7">
+        <v>2.9569</v>
+      </c>
       <c r="S21" s="7">
-        <v>2.9569</v>
-      </c>
-      <c r="T21" s="7">
         <v>0.722478</v>
       </c>
-      <c r="U21" s="11"/>
-      <c r="V21" s="7">
+      <c r="T21" s="14"/>
+      <c r="U21" s="7">
         <v>0.75206</v>
       </c>
-      <c r="W21" s="24">
+      <c r="V21" s="26">
         <v>3.78982</v>
       </c>
+      <c r="W21" s="7">
+        <v>4.92334</v>
+      </c>
       <c r="X21" s="7">
-        <v>4.92334</v>
-      </c>
-      <c r="Y21" s="7">
         <v>-2.31106</v>
       </c>
-      <c r="Z21" s="11"/>
-      <c r="AA21" s="7">
+      <c r="Y21" s="14"/>
+      <c r="Z21" s="7">
         <v>0.75206</v>
       </c>
-      <c r="AB21" s="24">
+      <c r="AA21" s="26">
         <v>3.26361</v>
       </c>
+      <c r="AB21" s="7">
+        <v>3.87809</v>
+      </c>
       <c r="AC21" s="7">
-        <v>3.87809</v>
-      </c>
-      <c r="AD21" s="7">
         <v>-1.49284</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="22" customHeight="1" ht="18.75">
-      <c r="A22" s="11"/>
-      <c r="B22" s="7">
+      <c r="A22" s="7">
         <v>0.80139</v>
       </c>
-      <c r="C22" s="24">
+      <c r="B22" s="26">
         <v>6.0381</v>
       </c>
+      <c r="C22" s="7">
+        <v>3.90348</v>
+      </c>
       <c r="D22" s="7">
-        <v>3.90348</v>
-      </c>
-      <c r="E22" s="7">
         <v>0.590187</v>
       </c>
-      <c r="F22" s="11"/>
-      <c r="G22" s="7">
+      <c r="E22" s="14"/>
+      <c r="F22" s="7">
         <v>0.80139</v>
       </c>
-      <c r="H22" s="24">
+      <c r="G22" s="26">
         <v>5.45569</v>
       </c>
+      <c r="H22" s="7">
+        <v>6.44247</v>
+      </c>
       <c r="I22" s="7">
-        <v>6.44247</v>
-      </c>
-      <c r="J22" s="7">
         <v>-2.92701</v>
       </c>
-      <c r="K22" s="11"/>
-      <c r="L22" s="7">
+      <c r="J22" s="14"/>
+      <c r="K22" s="7">
         <v>0.80139</v>
       </c>
-      <c r="M22" s="24">
+      <c r="L22" s="26">
         <v>4.64393</v>
       </c>
+      <c r="M22" s="7">
+        <v>5.33813</v>
+      </c>
       <c r="N22" s="7">
-        <v>5.33813</v>
-      </c>
-      <c r="O22" s="7">
         <v>-2.16634</v>
       </c>
-      <c r="P22" s="11"/>
-      <c r="Q22" s="7">
+      <c r="O22" s="14"/>
+      <c r="P22" s="7">
         <v>0.80139</v>
       </c>
-      <c r="R22" s="24">
+      <c r="Q22" s="26">
         <v>4.3916</v>
       </c>
+      <c r="R22" s="7">
+        <v>3.05815</v>
+      </c>
       <c r="S22" s="7">
-        <v>3.05815</v>
-      </c>
-      <c r="T22" s="7">
         <v>0.757448</v>
       </c>
-      <c r="U22" s="11"/>
-      <c r="V22" s="7">
+      <c r="T22" s="14"/>
+      <c r="U22" s="7">
         <v>0.80139</v>
       </c>
-      <c r="W22" s="24">
+      <c r="V22" s="26">
         <v>3.85487</v>
       </c>
+      <c r="W22" s="7">
+        <v>5.03866</v>
+      </c>
       <c r="X22" s="7">
-        <v>5.03866</v>
-      </c>
-      <c r="Y22" s="7">
         <v>-2.32835</v>
       </c>
-      <c r="Z22" s="11"/>
-      <c r="AA22" s="7">
+      <c r="Y22" s="14"/>
+      <c r="Z22" s="7">
         <v>0.80139</v>
       </c>
-      <c r="AB22" s="24">
+      <c r="AA22" s="26">
         <v>3.3247</v>
       </c>
+      <c r="AB22" s="7">
+        <v>3.98297</v>
+      </c>
       <c r="AC22" s="7">
-        <v>3.98297</v>
-      </c>
-      <c r="AD22" s="7">
         <v>-1.50158</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="23" customHeight="1" ht="18.75">
-      <c r="A23" s="11"/>
-      <c r="B23" s="7">
+      <c r="A23" s="7">
         <v>0.85108</v>
       </c>
-      <c r="C23" s="24">
+      <c r="B23" s="26">
         <v>6.21445</v>
       </c>
+      <c r="C23" s="7">
+        <v>4.12092</v>
+      </c>
       <c r="D23" s="7">
-        <v>4.12092</v>
-      </c>
-      <c r="E23" s="7">
         <v>0.631946</v>
       </c>
-      <c r="F23" s="11"/>
-      <c r="G23" s="7">
+      <c r="E23" s="14"/>
+      <c r="F23" s="7">
         <v>0.85108</v>
       </c>
-      <c r="H23" s="24">
+      <c r="G23" s="26">
         <v>5.59624</v>
       </c>
+      <c r="H23" s="7">
+        <v>6.69032</v>
+      </c>
       <c r="I23" s="7">
-        <v>6.69032</v>
-      </c>
-      <c r="J23" s="7">
         <v>-2.98682</v>
       </c>
-      <c r="K23" s="11"/>
-      <c r="L23" s="7">
+      <c r="J23" s="14"/>
+      <c r="K23" s="7">
         <v>0.85108</v>
       </c>
-      <c r="M23" s="24">
+      <c r="L23" s="26">
         <v>4.77759</v>
       </c>
+      <c r="M23" s="7">
+        <v>5.57183</v>
+      </c>
       <c r="N23" s="7">
-        <v>5.57183</v>
-      </c>
-      <c r="O23" s="7">
         <v>-2.21339</v>
       </c>
-      <c r="P23" s="11"/>
-      <c r="Q23" s="7">
+      <c r="O23" s="14"/>
+      <c r="P23" s="7">
         <v>0.85108</v>
       </c>
-      <c r="R23" s="24">
+      <c r="Q23" s="26">
         <v>4.52008</v>
       </c>
+      <c r="R23" s="7">
+        <v>3.22796</v>
+      </c>
       <c r="S23" s="7">
-        <v>3.22796</v>
-      </c>
-      <c r="T23" s="7">
         <v>0.814156</v>
       </c>
-      <c r="U23" s="11"/>
-      <c r="V23" s="7">
+      <c r="T23" s="14"/>
+      <c r="U23" s="7">
         <v>0.85108</v>
       </c>
-      <c r="W23" s="24">
+      <c r="V23" s="26">
         <v>3.96079</v>
       </c>
+      <c r="W23" s="7">
+        <v>5.22952</v>
+      </c>
       <c r="X23" s="7">
-        <v>5.22952</v>
-      </c>
-      <c r="Y23" s="7">
         <v>-2.35649</v>
       </c>
-      <c r="Z23" s="11"/>
-      <c r="AA23" s="7">
+      <c r="Y23" s="14"/>
+      <c r="Z23" s="7">
         <v>0.85108</v>
       </c>
-      <c r="AB23" s="24">
+      <c r="AA23" s="26">
         <v>3.4245</v>
       </c>
+      <c r="AB23" s="7">
+        <v>4.15756</v>
+      </c>
       <c r="AC23" s="7">
-        <v>4.15756</v>
-      </c>
-      <c r="AD23" s="7">
         <v>-1.51627</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="24" customHeight="1" ht="18.75">
-      <c r="A24" s="11"/>
-      <c r="B24" s="7">
+      <c r="A24" s="7">
         <v>0.90339</v>
       </c>
-      <c r="C24" s="24">
+      <c r="B24" s="26">
         <v>6.38031</v>
       </c>
+      <c r="C24" s="7">
+        <v>4.32728</v>
+      </c>
       <c r="D24" s="7">
-        <v>4.32728</v>
-      </c>
-      <c r="E24" s="7">
         <v>0.669716</v>
       </c>
-      <c r="F24" s="11"/>
-      <c r="G24" s="7">
+      <c r="E24" s="14"/>
+      <c r="F24" s="7">
         <v>0.90339</v>
       </c>
-      <c r="H24" s="24">
+      <c r="G24" s="26">
         <v>5.72784</v>
       </c>
+      <c r="H24" s="7">
+        <v>6.92397</v>
+      </c>
       <c r="I24" s="7">
-        <v>6.92397</v>
-      </c>
-      <c r="J24" s="7">
         <v>-3.04391</v>
       </c>
-      <c r="K24" s="11"/>
-      <c r="L24" s="7">
+      <c r="J24" s="14"/>
+      <c r="K24" s="7">
         <v>0.90339</v>
       </c>
-      <c r="M24" s="24">
+      <c r="L24" s="26">
         <v>4.90308</v>
       </c>
+      <c r="M24" s="7">
+        <v>5.79251</v>
+      </c>
       <c r="N24" s="7">
-        <v>5.79251</v>
-      </c>
-      <c r="O24" s="7">
         <v>-2.25836</v>
       </c>
-      <c r="P24" s="11"/>
-      <c r="Q24" s="7">
+      <c r="O24" s="14"/>
+      <c r="P24" s="7">
         <v>0.90339</v>
       </c>
-      <c r="R24" s="24">
+      <c r="Q24" s="26">
         <v>4.64105</v>
       </c>
+      <c r="R24" s="7">
+        <v>3.39074</v>
+      </c>
       <c r="S24" s="7">
-        <v>3.39074</v>
-      </c>
-      <c r="T24" s="7">
         <v>0.867079</v>
       </c>
-      <c r="U24" s="11"/>
-      <c r="V24" s="7">
+      <c r="T24" s="14"/>
+      <c r="U24" s="7">
         <v>0.90339</v>
       </c>
-      <c r="W24" s="24">
+      <c r="V24" s="26">
         <v>4.06021</v>
       </c>
+      <c r="W24" s="7">
+        <v>5.4109</v>
+      </c>
       <c r="X24" s="7">
-        <v>5.4109</v>
-      </c>
-      <c r="Y24" s="7">
         <v>-2.38345</v>
       </c>
-      <c r="Z24" s="11"/>
-      <c r="AA24" s="7">
+      <c r="Y24" s="14"/>
+      <c r="Z24" s="7">
         <v>0.90339</v>
       </c>
-      <c r="AB24" s="24">
+      <c r="AA24" s="26">
         <v>3.51837</v>
       </c>
+      <c r="AB24" s="7">
+        <v>4.324</v>
+      </c>
       <c r="AC24" s="7">
-        <v>4.324</v>
-      </c>
-      <c r="AD24" s="7">
         <v>-1.53072</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="25" customHeight="1" ht="18.75">
-      <c r="A25" s="11"/>
-      <c r="B25" s="7">
+      <c r="A25" s="7">
         <v>0.95085</v>
       </c>
-      <c r="C25" s="24">
+      <c r="B25" s="26">
         <v>6.51656</v>
       </c>
+      <c r="C25" s="7">
+        <v>4.50106</v>
+      </c>
       <c r="D25" s="7">
-        <v>4.50106</v>
-      </c>
-      <c r="E25" s="7">
         <v>0.699695</v>
       </c>
-      <c r="F25" s="11"/>
-      <c r="G25" s="7">
+      <c r="E25" s="14"/>
+      <c r="F25" s="7">
         <v>0.95085</v>
       </c>
-      <c r="H25" s="24">
+      <c r="G25" s="26">
         <v>5.83533</v>
       </c>
+      <c r="H25" s="7">
+        <v>7.11957</v>
+      </c>
       <c r="I25" s="7">
-        <v>7.11957</v>
-      </c>
-      <c r="J25" s="7">
         <v>-3.09188</v>
       </c>
-      <c r="K25" s="11"/>
-      <c r="L25" s="7">
+      <c r="J25" s="14"/>
+      <c r="K25" s="7">
         <v>0.95085</v>
       </c>
-      <c r="M25" s="24">
+      <c r="L25" s="26">
         <v>5.00543</v>
       </c>
+      <c r="M25" s="7">
+        <v>5.97752</v>
+      </c>
       <c r="N25" s="7">
-        <v>5.97752</v>
-      </c>
-      <c r="O25" s="7">
         <v>-2.29696</v>
       </c>
-      <c r="P25" s="11"/>
-      <c r="Q25" s="7">
+      <c r="O25" s="14"/>
+      <c r="P25" s="7">
         <v>0.95085</v>
       </c>
-      <c r="R25" s="24">
+      <c r="Q25" s="26">
         <v>4.73996</v>
       </c>
+      <c r="R25" s="7">
+        <v>3.52745</v>
+      </c>
       <c r="S25" s="7">
-        <v>3.52745</v>
-      </c>
-      <c r="T25" s="7">
         <v>0.910152</v>
       </c>
-      <c r="U25" s="11"/>
-      <c r="V25" s="7">
+      <c r="T25" s="14"/>
+      <c r="U25" s="7">
         <v>0.95085</v>
       </c>
-      <c r="W25" s="24">
+      <c r="V25" s="26">
         <v>4.14102</v>
       </c>
+      <c r="W25" s="7">
+        <v>5.56301</v>
+      </c>
       <c r="X25" s="7">
-        <v>5.56301</v>
-      </c>
-      <c r="Y25" s="7">
         <v>-2.40611</v>
       </c>
-      <c r="Z25" s="11"/>
-      <c r="AA25" s="7">
+      <c r="Y25" s="14"/>
+      <c r="Z25" s="7">
         <v>0.95085</v>
       </c>
-      <c r="AB25" s="24">
+      <c r="AA25" s="26">
         <v>3.59445</v>
       </c>
+      <c r="AB25" s="7">
+        <v>4.46351</v>
+      </c>
       <c r="AC25" s="7">
-        <v>4.46351</v>
-      </c>
-      <c r="AD25" s="7">
         <v>-1.54353</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="26" customHeight="1" ht="18.75">
-      <c r="A26" s="11"/>
-      <c r="B26" s="6">
+      <c r="A26" s="6">
         <v>1</v>
       </c>
-      <c r="C26" s="24">
+      <c r="B26" s="26">
         <v>6.65795</v>
       </c>
+      <c r="C26" s="7">
+        <v>4.68248</v>
+      </c>
       <c r="D26" s="7">
-        <v>4.68248</v>
-      </c>
-      <c r="E26" s="7">
         <v>0.72905</v>
       </c>
-      <c r="F26" s="11"/>
-      <c r="G26" s="6">
+      <c r="E26" s="14"/>
+      <c r="F26" s="6">
         <v>1</v>
       </c>
-      <c r="H26" s="24">
+      <c r="G26" s="26">
         <v>5.94657</v>
       </c>
+      <c r="H26" s="7">
+        <v>7.3224</v>
+      </c>
       <c r="I26" s="7">
-        <v>7.3224</v>
-      </c>
-      <c r="J26" s="7">
         <v>-3.14281</v>
       </c>
-      <c r="K26" s="11"/>
-      <c r="L26" s="6">
+      <c r="J26" s="14"/>
+      <c r="K26" s="6">
         <v>1</v>
       </c>
-      <c r="M26" s="24">
+      <c r="L26" s="26">
         <v>5.11153</v>
       </c>
+      <c r="M26" s="7">
+        <v>6.16979</v>
+      </c>
       <c r="N26" s="7">
-        <v>6.16979</v>
-      </c>
-      <c r="O26" s="7">
         <v>-2.33866</v>
       </c>
-      <c r="P26" s="11"/>
-      <c r="Q26" s="6">
+      <c r="O26" s="14"/>
+      <c r="P26" s="6">
         <v>1</v>
       </c>
-      <c r="R26" s="24">
+      <c r="Q26" s="26">
         <v>4.84147</v>
       </c>
+      <c r="R26" s="7">
+        <v>3.66844</v>
+      </c>
       <c r="S26" s="7">
-        <v>3.66844</v>
-      </c>
-      <c r="T26" s="7">
         <v>0.95317</v>
       </c>
-      <c r="U26" s="11"/>
-      <c r="V26" s="6">
+      <c r="T26" s="14"/>
+      <c r="U26" s="6">
         <v>1</v>
       </c>
-      <c r="W26" s="24">
+      <c r="V26" s="26">
         <v>4.22364</v>
       </c>
+      <c r="W26" s="7">
+        <v>5.71956</v>
+      </c>
       <c r="X26" s="7">
-        <v>5.71956</v>
-      </c>
-      <c r="Y26" s="7">
         <v>-2.43062</v>
       </c>
-      <c r="Z26" s="11"/>
-      <c r="AA26" s="6">
+      <c r="Y26" s="14"/>
+      <c r="Z26" s="6">
         <v>1</v>
       </c>
-      <c r="AB26" s="24">
+      <c r="AA26" s="26">
         <v>3.67221</v>
       </c>
+      <c r="AB26" s="7">
+        <v>4.60708</v>
+      </c>
       <c r="AC26" s="7">
-        <v>4.60708</v>
-      </c>
-      <c r="AD26" s="7">
         <v>-1.55797</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="27" customHeight="1" ht="18.75">
-      <c r="A27" s="11"/>
+      <c r="A27" s="15"/>
       <c r="B27" s="12"/>
-      <c r="C27" s="13"/>
-      <c r="D27" s="13"/>
-      <c r="E27" s="13"/>
-      <c r="F27" s="11"/>
+      <c r="C27" s="12"/>
+      <c r="D27" s="12"/>
+      <c r="E27" s="14"/>
+      <c r="F27" s="15"/>
       <c r="G27" s="12"/>
-      <c r="H27" s="13"/>
-      <c r="I27" s="13"/>
-      <c r="J27" s="13"/>
-      <c r="K27" s="11"/>
+      <c r="H27" s="12"/>
+      <c r="I27" s="12"/>
+      <c r="J27" s="14"/>
+      <c r="K27" s="15"/>
       <c r="L27" s="12"/>
-      <c r="M27" s="13"/>
-      <c r="N27" s="13"/>
-      <c r="O27" s="13"/>
-      <c r="P27" s="11"/>
+      <c r="M27" s="12"/>
+      <c r="N27" s="12"/>
+      <c r="O27" s="14"/>
+      <c r="P27" s="15"/>
       <c r="Q27" s="12"/>
-      <c r="R27" s="13"/>
-      <c r="S27" s="13"/>
-      <c r="T27" s="13"/>
-      <c r="U27" s="11"/>
+      <c r="R27" s="12"/>
+      <c r="S27" s="12"/>
+      <c r="T27" s="14"/>
+      <c r="U27" s="15"/>
       <c r="V27" s="12"/>
-      <c r="W27" s="13"/>
-      <c r="X27" s="13"/>
-      <c r="Y27" s="13"/>
-      <c r="Z27" s="11"/>
+      <c r="W27" s="12"/>
+      <c r="X27" s="12"/>
+      <c r="Y27" s="14"/>
+      <c r="Z27" s="15"/>
       <c r="AA27" s="12"/>
-      <c r="AB27" s="13"/>
-      <c r="AC27" s="13"/>
-      <c r="AD27" s="13"/>
+      <c r="AB27" s="12"/>
+      <c r="AC27" s="12"/>
     </row>
     <row x14ac:dyDescent="0.25" r="28" customHeight="1" ht="18.75">
-      <c r="A28" s="11"/>
+      <c r="A28" s="15"/>
       <c r="B28" s="12"/>
-      <c r="C28" s="13"/>
-      <c r="D28" s="13"/>
-      <c r="E28" s="13"/>
-      <c r="F28" s="11"/>
+      <c r="C28" s="12"/>
+      <c r="D28" s="12"/>
+      <c r="E28" s="14"/>
+      <c r="F28" s="15"/>
       <c r="G28" s="12"/>
-      <c r="H28" s="13"/>
-      <c r="I28" s="13"/>
-      <c r="J28" s="13"/>
-      <c r="K28" s="11"/>
+      <c r="H28" s="12"/>
+      <c r="I28" s="12"/>
+      <c r="J28" s="14"/>
+      <c r="K28" s="15"/>
       <c r="L28" s="12"/>
-      <c r="M28" s="13"/>
-      <c r="N28" s="13"/>
-      <c r="O28" s="13"/>
-      <c r="P28" s="11"/>
+      <c r="M28" s="12"/>
+      <c r="N28" s="12"/>
+      <c r="O28" s="14"/>
+      <c r="P28" s="15"/>
       <c r="Q28" s="12"/>
-      <c r="R28" s="13"/>
-      <c r="S28" s="13"/>
-      <c r="T28" s="13"/>
-      <c r="U28" s="11"/>
+      <c r="R28" s="12"/>
+      <c r="S28" s="12"/>
+      <c r="T28" s="14"/>
+      <c r="U28" s="15"/>
       <c r="V28" s="12"/>
-      <c r="W28" s="13"/>
-      <c r="X28" s="13"/>
-      <c r="Y28" s="13"/>
-      <c r="Z28" s="11"/>
+      <c r="W28" s="12"/>
+      <c r="X28" s="12"/>
+      <c r="Y28" s="14"/>
+      <c r="Z28" s="15"/>
       <c r="AA28" s="12"/>
-      <c r="AB28" s="13"/>
-      <c r="AC28" s="13"/>
-      <c r="AD28" s="13"/>
+      <c r="AB28" s="12"/>
+      <c r="AC28" s="12"/>
     </row>
     <row x14ac:dyDescent="0.25" r="29" customHeight="1" ht="18.75">
-      <c r="A29" s="11"/>
+      <c r="A29" s="15"/>
       <c r="B29" s="12"/>
-      <c r="C29" s="13"/>
-      <c r="D29" s="13"/>
-      <c r="E29" s="13"/>
-      <c r="F29" s="11"/>
+      <c r="C29" s="12"/>
+      <c r="D29" s="12"/>
+      <c r="E29" s="14"/>
+      <c r="F29" s="15"/>
       <c r="G29" s="12"/>
-      <c r="H29" s="13"/>
-      <c r="I29" s="13"/>
-      <c r="J29" s="13"/>
-      <c r="K29" s="11"/>
+      <c r="H29" s="12"/>
+      <c r="I29" s="12"/>
+      <c r="J29" s="14"/>
+      <c r="K29" s="15"/>
       <c r="L29" s="12"/>
-      <c r="M29" s="13"/>
-      <c r="N29" s="13"/>
-      <c r="O29" s="13"/>
-      <c r="P29" s="11"/>
+      <c r="M29" s="12"/>
+      <c r="N29" s="12"/>
+      <c r="O29" s="14"/>
+      <c r="P29" s="15"/>
       <c r="Q29" s="12"/>
-      <c r="R29" s="13"/>
-      <c r="S29" s="13"/>
-      <c r="T29" s="13"/>
-      <c r="U29" s="11"/>
+      <c r="R29" s="12"/>
+      <c r="S29" s="12"/>
+      <c r="T29" s="14"/>
+      <c r="U29" s="15"/>
       <c r="V29" s="12"/>
-      <c r="W29" s="13"/>
-      <c r="X29" s="13"/>
-      <c r="Y29" s="13"/>
-      <c r="Z29" s="11"/>
+      <c r="W29" s="12"/>
+      <c r="X29" s="12"/>
+      <c r="Y29" s="14"/>
+      <c r="Z29" s="15"/>
       <c r="AA29" s="12"/>
-      <c r="AB29" s="13"/>
-      <c r="AC29" s="13"/>
-      <c r="AD29" s="13"/>
+      <c r="AB29" s="12"/>
+      <c r="AC29" s="12"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
